--- a/Data/Bronze/MCIC-PROFUNDIZACION/Procesos de Renocavion y acreditación/Plan de Mejoramiento/FACTOR 8. APORTES DE LA INVESTIGACIÓN, LA INNOVACIÓN, EL DESARROLLO TECNOLÓGICO Y LA CREACIÓN ASOCIADOS AL PROGRAMA ACADÉMICO/b. Socialización y vinculación de actividades de investigación/F8_Trabajos_de_grado_por_grupo_Profundizacion.xlsx
+++ b/Data/Bronze/MCIC-PROFUNDIZACION/Procesos de Renocavion y acreditación/Plan de Mejoramiento/FACTOR 8. APORTES DE LA INVESTIGACIÓN, LA INNOVACIÓN, EL DESARROLLO TECNOLÓGICO Y LA CREACIÓN ASOCIADOS AL PROGRAMA ACADÉMICO/b. Socialización y vinculación de actividades de investigación/F8_Trabajos_de_grado_por_grupo_Profundizacion.xlsx
@@ -1234,33 +1234,33 @@
     <row r="7">
       <c r="A7" s="6" t="inlineStr">
         <is>
-          <t>INTERNET INTELIGENTE</t>
+          <t>LIDER</t>
         </is>
       </c>
       <c r="B7" s="6" t="n">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="C7" s="6" t="n">
-        <v>8</v>
+        <v>3</v>
       </c>
       <c r="D7" s="6" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="12" t="inlineStr">
         <is>
-          <t>LIDER</t>
+          <t>INTERNET INTELIGENTE</t>
         </is>
       </c>
       <c r="B8" s="12" t="n">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="C8" s="12" t="n">
-        <v>3</v>
+        <v>8</v>
       </c>
       <c r="D8" s="12" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="9">
@@ -1298,14 +1298,14 @@
     <row r="11">
       <c r="A11" s="6" t="inlineStr">
         <is>
-          <t>GIIRA</t>
+          <t>Multimedia Interactiva y Animación Digital</t>
         </is>
       </c>
       <c r="B11" s="6" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="C11" s="6" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="D11" s="6" t="n">
         <v>1</v>
@@ -1330,14 +1330,14 @@
     <row r="13">
       <c r="A13" s="6" t="inlineStr">
         <is>
-          <t>Multimedia Interactiva y Animación Digital</t>
+          <t>GIIRA</t>
         </is>
       </c>
       <c r="B13" s="6" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="C13" s="6" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="D13" s="6" t="n">
         <v>1</v>
@@ -1346,7 +1346,7 @@
     <row r="14">
       <c r="A14" s="12" t="inlineStr">
         <is>
-          <t>INTECSE</t>
+          <t>GITUD</t>
         </is>
       </c>
       <c r="B14" s="12" t="n">
@@ -1362,7 +1362,7 @@
     <row r="15">
       <c r="A15" s="6" t="inlineStr">
         <is>
-          <t>GITUD</t>
+          <t>INTECSE</t>
         </is>
       </c>
       <c r="B15" s="6" t="n">
@@ -1426,7 +1426,7 @@
     <row r="19">
       <c r="A19" s="6" t="inlineStr">
         <is>
-          <t>GICOECOL</t>
+          <t>ARMOS</t>
         </is>
       </c>
       <c r="B19" s="6" t="n">
@@ -1442,7 +1442,7 @@
     <row r="20">
       <c r="A20" s="12" t="inlineStr">
         <is>
-          <t>ARMOS</t>
+          <t>GICOECOL</t>
         </is>
       </c>
       <c r="B20" s="12" t="n">
@@ -1474,14 +1474,14 @@
     <row r="22">
       <c r="A22" s="12" t="inlineStr">
         <is>
-          <t>LASER LAMIC</t>
+          <t>GITEM++</t>
         </is>
       </c>
       <c r="B22" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="C22" s="12" t="n">
         <v>1</v>
-      </c>
-      <c r="C22" s="12" t="n">
-        <v>0</v>
       </c>
       <c r="D22" s="12" t="n">
         <v>0</v>
@@ -1490,14 +1490,14 @@
     <row r="23">
       <c r="A23" s="6" t="inlineStr">
         <is>
-          <t>XUE</t>
+          <t>CEPMS</t>
         </is>
       </c>
       <c r="B23" s="6" t="n">
+        <v>1</v>
+      </c>
+      <c r="C23" s="6" t="n">
         <v>0</v>
-      </c>
-      <c r="C23" s="6" t="n">
-        <v>1</v>
       </c>
       <c r="D23" s="6" t="n">
         <v>0</v>
@@ -1506,14 +1506,14 @@
     <row r="24">
       <c r="A24" s="12" t="inlineStr">
         <is>
-          <t>COMPLEX UD</t>
+          <t>DIMSI</t>
         </is>
       </c>
       <c r="B24" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="C24" s="12" t="n">
         <v>1</v>
-      </c>
-      <c r="C24" s="12" t="n">
-        <v>0</v>
       </c>
       <c r="D24" s="12" t="n">
         <v>0</v>
@@ -1522,7 +1522,7 @@
     <row r="25">
       <c r="A25" s="6" t="inlineStr">
         <is>
-          <t>LAMIC</t>
+          <t>PROPROBOS</t>
         </is>
       </c>
       <c r="B25" s="6" t="n">
@@ -1538,7 +1538,7 @@
     <row r="26">
       <c r="A26" s="12" t="inlineStr">
         <is>
-          <t>PROPROBOS</t>
+          <t>LASER LAMIC</t>
         </is>
       </c>
       <c r="B26" s="12" t="n">
@@ -1554,7 +1554,7 @@
     <row r="27">
       <c r="A27" s="6" t="inlineStr">
         <is>
-          <t>CEPMS</t>
+          <t>Bionanotecnología</t>
         </is>
       </c>
       <c r="B27" s="6" t="n">
@@ -1570,7 +1570,7 @@
     <row r="28">
       <c r="A28" s="12" t="inlineStr">
         <is>
-          <t>Bionanotecnología</t>
+          <t>COMPLEX UD</t>
         </is>
       </c>
       <c r="B28" s="12" t="n">
@@ -1586,14 +1586,14 @@
     <row r="29">
       <c r="A29" s="6" t="inlineStr">
         <is>
-          <t>DIMSI</t>
+          <t>LAMIC</t>
         </is>
       </c>
       <c r="B29" s="6" t="n">
+        <v>1</v>
+      </c>
+      <c r="C29" s="6" t="n">
         <v>0</v>
-      </c>
-      <c r="C29" s="6" t="n">
-        <v>1</v>
       </c>
       <c r="D29" s="6" t="n">
         <v>0</v>
@@ -1602,7 +1602,7 @@
     <row r="30">
       <c r="A30" s="12" t="inlineStr">
         <is>
-          <t>GITEM++</t>
+          <t>XUE</t>
         </is>
       </c>
       <c r="B30" s="12" t="n">

--- a/Data/Bronze/MCIC-PROFUNDIZACION/Procesos de Renocavion y acreditación/Plan de Mejoramiento/FACTOR 8. APORTES DE LA INVESTIGACIÓN, LA INNOVACIÓN, EL DESARROLLO TECNOLÓGICO Y LA CREACIÓN ASOCIADOS AL PROGRAMA ACADÉMICO/b. Socialización y vinculación de actividades de investigación/F8_Trabajos_de_grado_por_grupo_Profundizacion.xlsx
+++ b/Data/Bronze/MCIC-PROFUNDIZACION/Procesos de Renocavion y acreditación/Plan de Mejoramiento/FACTOR 8. APORTES DE LA INVESTIGACIÓN, LA INNOVACIÓN, EL DESARROLLO TECNOLÓGICO Y LA CREACIÓN ASOCIADOS AL PROGRAMA ACADÉMICO/b. Socialización y vinculación de actividades de investigación/F8_Trabajos_de_grado_por_grupo_Profundizacion.xlsx
@@ -11,13 +11,11 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Comparativo por grupo" sheetId="2" state="visible" r:id="rId2"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Consolidado" sheetId="3" state="visible" r:id="rId3"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Pendientes sustentación" sheetId="4" state="visible" r:id="rId4"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Modalidad por confirmar" sheetId="5" state="visible" r:id="rId5"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Fuentes y calidad" sheetId="6" state="visible" r:id="rId6"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Fuentes y calidad" sheetId="5" state="visible" r:id="rId5"/>
   </sheets>
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'Consolidado'!$A$3:$M$58</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'Pendientes sustentación'!$A$3:$M$11</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="4" hidden="1">'Modalidad por confirmar'!$A$4:$M$23</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -26,7 +24,7 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="9">
+  <fonts count="8">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -74,14 +72,8 @@
       <color rgb="000B3B60"/>
       <sz val="18"/>
     </font>
-    <font>
-      <name val="Calibri"/>
-      <i val="1"/>
-      <color rgb="004B5563"/>
-      <sz val="9.5"/>
-    </font>
   </fonts>
-  <fills count="6">
+  <fills count="5">
     <fill>
       <patternFill/>
     </fill>
@@ -96,11 +88,6 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="00DCE6F1"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="00FFF4E5"/>
       </patternFill>
     </fill>
     <fill>
@@ -179,7 +166,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="13">
+  <cellXfs count="12">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
@@ -200,13 +187,10 @@
     <xf numFmtId="0" fontId="7" fillId="3" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="4" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="4" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="5" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -574,7 +558,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H49"/>
+  <dimension ref="A1:H47"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="17" customWidth="1" min="1" max="1"/>
@@ -698,362 +682,353 @@
         <v>17</v>
       </c>
     </row>
-    <row r="13" ht="39" customHeight="1">
-      <c r="A13" s="10" t="inlineStr">
-        <is>
-          <t>Modalidad: la del consolidado; si falta, se completa por código o por nombre del estudiante (Cóndor y bases MCIC, marcado como «Inferida por nombre» en la columna «Nota de modalidad»: 11 casos por verificar). Quedan 19 casos sin modalidad (hoja «Modalidad por confirmar», la misma en ambas modalidades). Pasantía se clasifica como Profundización.</t>
-        </is>
-      </c>
-    </row>
-    <row r="16">
-      <c r="A16" s="3" t="inlineStr">
+    <row r="15">
+      <c r="A15" s="3" t="inlineStr">
         <is>
           <t>Proyectos de investigación y de profundización (comparativo)</t>
         </is>
       </c>
     </row>
-    <row r="17" ht="30" customHeight="1">
-      <c r="A17" s="11" t="inlineStr">
+    <row r="16" ht="30" customHeight="1">
+      <c r="A16" s="10" t="inlineStr">
         <is>
           <t>Modalidad</t>
         </is>
       </c>
-      <c r="B17" s="11" t="inlineStr">
+      <c r="B16" s="10" t="inlineStr">
         <is>
           <t>Trabajos</t>
         </is>
       </c>
-      <c r="C17" s="11" t="inlineStr">
+      <c r="C16" s="10" t="inlineStr">
         <is>
           <t>Sustentados</t>
         </is>
       </c>
-      <c r="D17" s="11" t="inlineStr">
+      <c r="D16" s="10" t="inlineStr">
         <is>
           <t>No sustentados</t>
         </is>
       </c>
-      <c r="E17" s="11" t="inlineStr">
+      <c r="E16" s="10" t="inlineStr">
         <is>
           <t>Grupos distintos</t>
         </is>
       </c>
-      <c r="F17" s="11" t="inlineStr">
+      <c r="F16" s="10" t="inlineStr">
         <is>
           <t>Pasantías</t>
         </is>
       </c>
     </row>
+    <row r="17">
+      <c r="A17" s="6" t="inlineStr">
+        <is>
+          <t>Investigación</t>
+        </is>
+      </c>
+      <c r="B17" s="6" t="n">
+        <v>93</v>
+      </c>
+      <c r="C17" s="6" t="n">
+        <v>86</v>
+      </c>
+      <c r="D17" s="6" t="n">
+        <v>7</v>
+      </c>
+      <c r="E17" s="6" t="n">
+        <v>22</v>
+      </c>
+      <c r="F17" s="6" t="n">
+        <v>0</v>
+      </c>
+    </row>
     <row r="18">
-      <c r="A18" s="6" t="inlineStr">
-        <is>
-          <t>Investigación</t>
-        </is>
-      </c>
-      <c r="B18" s="6" t="n">
-        <v>74</v>
-      </c>
-      <c r="C18" s="6" t="n">
-        <v>67</v>
-      </c>
-      <c r="D18" s="6" t="n">
-        <v>7</v>
-      </c>
-      <c r="E18" s="6" t="n">
-        <v>22</v>
-      </c>
-      <c r="F18" s="6" t="n">
+      <c r="A18" s="11" t="inlineStr">
+        <is>
+          <t>Profundización</t>
+        </is>
+      </c>
+      <c r="B18" s="11" t="n">
+        <v>55</v>
+      </c>
+      <c r="C18" s="11" t="n">
+        <v>47</v>
+      </c>
+      <c r="D18" s="11" t="n">
+        <v>8</v>
+      </c>
+      <c r="E18" s="11" t="n">
+        <v>17</v>
+      </c>
+      <c r="F18" s="11" t="n">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="6" t="inlineStr">
+        <is>
+          <t>Total consolidado</t>
+        </is>
+      </c>
+      <c r="B19" s="6" t="n">
+        <v>148</v>
+      </c>
+      <c r="C19" s="6" t="n">
+        <v>133</v>
+      </c>
+      <c r="D19" s="6" t="n">
+        <v>15</v>
+      </c>
+      <c r="E19" s="6" t="n">
+        <v>26</v>
+      </c>
+      <c r="F19" s="6" t="n">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="3" t="inlineStr">
+        <is>
+          <t>Por año — Profundización</t>
+        </is>
+      </c>
+    </row>
+    <row r="22" ht="30" customHeight="1">
+      <c r="A22" s="10" t="inlineStr">
+        <is>
+          <t>Año</t>
+        </is>
+      </c>
+      <c r="B22" s="10" t="inlineStr">
+        <is>
+          <t>Sustentados</t>
+        </is>
+      </c>
+      <c r="C22" s="10" t="inlineStr">
+        <is>
+          <t>No sustentados</t>
+        </is>
+      </c>
+      <c r="D22" s="10" t="inlineStr">
+        <is>
+          <t>Total</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="6" t="n">
+        <v>2022</v>
+      </c>
+      <c r="B23" s="6" t="n">
+        <v>8</v>
+      </c>
+      <c r="C23" s="6" t="n">
         <v>0</v>
       </c>
-    </row>
-    <row r="19">
-      <c r="A19" s="12" t="inlineStr">
-        <is>
-          <t>Profundización</t>
-        </is>
-      </c>
-      <c r="B19" s="12" t="n">
-        <v>55</v>
-      </c>
-      <c r="C19" s="12" t="n">
-        <v>47</v>
-      </c>
-      <c r="D19" s="12" t="n">
+      <c r="D23" s="6" t="n">
         <v>8</v>
       </c>
-      <c r="E19" s="12" t="n">
-        <v>17</v>
-      </c>
-      <c r="F19" s="12" t="n">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="20">
-      <c r="A20" s="6" t="inlineStr">
-        <is>
-          <t>Por confirmar</t>
-        </is>
-      </c>
-      <c r="B20" s="6" t="n">
-        <v>19</v>
-      </c>
-      <c r="C20" s="6" t="n">
-        <v>19</v>
-      </c>
-      <c r="D20" s="6" t="n">
+    </row>
+    <row r="24">
+      <c r="A24" s="11" t="n">
+        <v>2023</v>
+      </c>
+      <c r="B24" s="11" t="n">
+        <v>8</v>
+      </c>
+      <c r="C24" s="11" t="n">
         <v>0</v>
       </c>
-      <c r="E20" s="6" t="n">
-        <v>7</v>
-      </c>
-      <c r="F20" s="6" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="21">
-      <c r="A21" s="12" t="inlineStr">
-        <is>
-          <t>Total consolidado</t>
-        </is>
-      </c>
-      <c r="B21" s="12" t="n">
-        <v>148</v>
-      </c>
-      <c r="C21" s="12" t="n">
-        <v>133</v>
-      </c>
-      <c r="D21" s="12" t="n">
-        <v>15</v>
-      </c>
-      <c r="E21" s="12" t="n">
-        <v>26</v>
-      </c>
-      <c r="F21" s="12" t="n">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="23">
-      <c r="A23" s="3" t="inlineStr">
-        <is>
-          <t>Por año — Profundización</t>
-        </is>
-      </c>
-    </row>
-    <row r="24" ht="30" customHeight="1">
-      <c r="A24" s="11" t="inlineStr">
-        <is>
-          <t>Año</t>
-        </is>
-      </c>
-      <c r="B24" s="11" t="inlineStr">
-        <is>
-          <t>Sustentados</t>
-        </is>
-      </c>
-      <c r="C24" s="11" t="inlineStr">
-        <is>
-          <t>No sustentados</t>
-        </is>
-      </c>
-      <c r="D24" s="11" t="inlineStr">
-        <is>
-          <t>Total</t>
-        </is>
+      <c r="D24" s="11" t="n">
+        <v>8</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" s="6" t="n">
-        <v>2022</v>
+        <v>2024</v>
       </c>
       <c r="B25" s="6" t="n">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="C25" s="6" t="n">
         <v>0</v>
       </c>
       <c r="D25" s="6" t="n">
-        <v>8</v>
+        <v>6</v>
       </c>
     </row>
     <row r="26">
-      <c r="A26" s="12" t="n">
-        <v>2023</v>
-      </c>
-      <c r="B26" s="12" t="n">
-        <v>8</v>
-      </c>
-      <c r="C26" s="12" t="n">
+      <c r="A26" s="11" t="n">
+        <v>2025</v>
+      </c>
+      <c r="B26" s="11" t="n">
+        <v>16</v>
+      </c>
+      <c r="C26" s="11" t="n">
         <v>0</v>
       </c>
-      <c r="D26" s="12" t="n">
-        <v>8</v>
+      <c r="D26" s="11" t="n">
+        <v>16</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" s="6" t="n">
-        <v>2024</v>
+        <v>2026</v>
       </c>
       <c r="B27" s="6" t="n">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="C27" s="6" t="n">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="D27" s="6" t="n">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="28">
-      <c r="A28" s="12" t="n">
-        <v>2025</v>
-      </c>
-      <c r="B28" s="12" t="n">
-        <v>16</v>
-      </c>
-      <c r="C28" s="12" t="n">
-        <v>0</v>
-      </c>
-      <c r="D28" s="12" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
     </row>
     <row r="29">
-      <c r="A29" s="6" t="n">
-        <v>2026</v>
-      </c>
-      <c r="B29" s="6" t="n">
+      <c r="A29" s="3" t="inlineStr">
+        <is>
+          <t>Por grupo de investigación — Profundización</t>
+        </is>
+      </c>
+    </row>
+    <row r="30" ht="30" customHeight="1">
+      <c r="A30" s="10" t="inlineStr">
+        <is>
+          <t>Grupo</t>
+        </is>
+      </c>
+      <c r="B30" s="10" t="inlineStr">
+        <is>
+          <t>Trabajos de grado</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" s="6" t="inlineStr">
+        <is>
+          <t>NIDE</t>
+        </is>
+      </c>
+      <c r="B31" s="6" t="n">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" s="11" t="inlineStr">
+        <is>
+          <t>GEFEM</t>
+        </is>
+      </c>
+      <c r="B32" s="11" t="n">
         <v>9</v>
-      </c>
-      <c r="C29" s="6" t="n">
-        <v>8</v>
-      </c>
-      <c r="D29" s="6" t="n">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="31">
-      <c r="A31" s="3" t="inlineStr">
-        <is>
-          <t>Por grupo de investigación — Profundización</t>
-        </is>
-      </c>
-    </row>
-    <row r="32" ht="30" customHeight="1">
-      <c r="A32" s="11" t="inlineStr">
-        <is>
-          <t>Grupo</t>
-        </is>
-      </c>
-      <c r="B32" s="11" t="inlineStr">
-        <is>
-          <t>Trabajos de grado</t>
-        </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" s="6" t="inlineStr">
         <is>
-          <t>NIDE</t>
+          <t>INTERNET INTELIGENTE</t>
         </is>
       </c>
       <c r="B33" s="6" t="n">
-        <v>11</v>
+        <v>8</v>
       </c>
     </row>
     <row r="34">
-      <c r="A34" s="12" t="inlineStr">
-        <is>
-          <t>GEFEM</t>
-        </is>
-      </c>
-      <c r="B34" s="12" t="n">
-        <v>9</v>
+      <c r="A34" s="11" t="inlineStr">
+        <is>
+          <t>Multimedia Interactiva y Animación Digital</t>
+        </is>
+      </c>
+      <c r="B34" s="11" t="n">
+        <v>4</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" s="6" t="inlineStr">
         <is>
-          <t>INTERNET INTELIGENTE</t>
+          <t>GITEM</t>
         </is>
       </c>
       <c r="B35" s="6" t="n">
-        <v>8</v>
+        <v>4</v>
       </c>
     </row>
     <row r="36">
-      <c r="A36" s="12" t="inlineStr">
-        <is>
-          <t>Multimedia Interactiva y Animación Digital</t>
-        </is>
-      </c>
-      <c r="B36" s="12" t="n">
-        <v>4</v>
+      <c r="A36" s="11" t="inlineStr">
+        <is>
+          <t>GESETIC</t>
+        </is>
+      </c>
+      <c r="B36" s="11" t="n">
+        <v>3</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" s="6" t="inlineStr">
         <is>
-          <t>GITEM</t>
+          <t>LIDER</t>
         </is>
       </c>
       <c r="B37" s="6" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
     </row>
     <row r="38">
-      <c r="A38" s="12" t="inlineStr">
-        <is>
-          <t>GESETIC</t>
-        </is>
-      </c>
-      <c r="B38" s="12" t="n">
-        <v>3</v>
+      <c r="A38" s="11" t="inlineStr">
+        <is>
+          <t>GICOGE</t>
+        </is>
+      </c>
+      <c r="B38" s="11" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" s="6" t="inlineStr">
         <is>
-          <t>LIDER</t>
+          <t>GIIRA</t>
         </is>
       </c>
       <c r="B39" s="6" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="40">
-      <c r="A40" s="12" t="inlineStr">
-        <is>
-          <t>GICOGE</t>
-        </is>
-      </c>
-      <c r="B40" s="12" t="n">
+      <c r="A40" s="11" t="inlineStr">
+        <is>
+          <t>LASER</t>
+        </is>
+      </c>
+      <c r="B40" s="11" t="n">
         <v>2</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" s="6" t="inlineStr">
         <is>
-          <t>GIIRA</t>
+          <t>GRECO</t>
         </is>
       </c>
       <c r="B41" s="6" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="42">
-      <c r="A42" s="12" t="inlineStr">
-        <is>
-          <t>LASER</t>
-        </is>
-      </c>
-      <c r="B42" s="12" t="n">
-        <v>2</v>
+      <c r="A42" s="11" t="inlineStr">
+        <is>
+          <t>IAFT</t>
+        </is>
+      </c>
+      <c r="B42" s="11" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="43">
       <c r="A43" s="6" t="inlineStr">
         <is>
-          <t>GRECO</t>
+          <t>DIMSI</t>
         </is>
       </c>
       <c r="B43" s="6" t="n">
@@ -1061,19 +1036,19 @@
       </c>
     </row>
     <row r="44">
-      <c r="A44" s="12" t="inlineStr">
-        <is>
-          <t>IAFT</t>
-        </is>
-      </c>
-      <c r="B44" s="12" t="n">
+      <c r="A44" s="11" t="inlineStr">
+        <is>
+          <t>GICOECOL</t>
+        </is>
+      </c>
+      <c r="B44" s="11" t="n">
         <v>1</v>
       </c>
     </row>
     <row r="45">
       <c r="A45" s="6" t="inlineStr">
         <is>
-          <t>DIMSI</t>
+          <t>XUE</t>
         </is>
       </c>
       <c r="B45" s="6" t="n">
@@ -1081,68 +1056,47 @@
       </c>
     </row>
     <row r="46">
-      <c r="A46" s="12" t="inlineStr">
-        <is>
-          <t>GICOECOL</t>
-        </is>
-      </c>
-      <c r="B46" s="12" t="n">
+      <c r="A46" s="11" t="inlineStr">
+        <is>
+          <t>ARMOS</t>
+        </is>
+      </c>
+      <c r="B46" s="11" t="n">
         <v>1</v>
       </c>
     </row>
     <row r="47">
       <c r="A47" s="6" t="inlineStr">
         <is>
-          <t>XUE</t>
+          <t>GITEM++</t>
         </is>
       </c>
       <c r="B47" s="6" t="n">
         <v>1</v>
       </c>
     </row>
-    <row r="48">
-      <c r="A48" s="12" t="inlineStr">
-        <is>
-          <t>ARMOS</t>
-        </is>
-      </c>
-      <c r="B48" s="12" t="n">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="49">
-      <c r="A49" s="6" t="inlineStr">
-        <is>
-          <t>GITEM++</t>
-        </is>
-      </c>
-      <c r="B49" s="6" t="n">
-        <v>1</v>
-      </c>
-    </row>
   </sheetData>
-  <mergeCells count="21">
+  <mergeCells count="20">
+    <mergeCell ref="A15:H15"/>
     <mergeCell ref="A1:H1"/>
     <mergeCell ref="A6:B6"/>
     <mergeCell ref="C10:D10"/>
     <mergeCell ref="A7:B7"/>
     <mergeCell ref="E10:F10"/>
     <mergeCell ref="G10:H10"/>
-    <mergeCell ref="A16:H16"/>
     <mergeCell ref="C9:D9"/>
     <mergeCell ref="E9:F9"/>
     <mergeCell ref="C7:H7"/>
+    <mergeCell ref="A21:H21"/>
     <mergeCell ref="A2:H2"/>
     <mergeCell ref="A5:B5"/>
-    <mergeCell ref="A23:H23"/>
     <mergeCell ref="A4:H4"/>
     <mergeCell ref="C6:H6"/>
+    <mergeCell ref="A29:H29"/>
     <mergeCell ref="C5:H5"/>
     <mergeCell ref="A10:B10"/>
-    <mergeCell ref="A13:H13"/>
     <mergeCell ref="A9:B9"/>
     <mergeCell ref="G9:H9"/>
-    <mergeCell ref="A31:H31"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -1160,7 +1114,6 @@
     <col width="50" customWidth="1" min="1" max="1"/>
     <col width="16" customWidth="1" min="2" max="2"/>
     <col width="16" customWidth="1" min="3" max="3"/>
-    <col width="22" customWidth="1" min="4" max="4"/>
   </cols>
   <sheetData>
     <row r="1" ht="24" customHeight="1">
@@ -1178,24 +1131,19 @@
       </c>
     </row>
     <row r="4" ht="30" customHeight="1">
-      <c r="A4" s="11" t="inlineStr">
+      <c r="A4" s="10" t="inlineStr">
         <is>
           <t>Grupo de investigación</t>
         </is>
       </c>
-      <c r="B4" s="11" t="inlineStr">
+      <c r="B4" s="10" t="inlineStr">
         <is>
           <t>Investigación</t>
         </is>
       </c>
-      <c r="C4" s="11" t="inlineStr">
-        <is>
-          <t>Profundización</t>
-        </is>
-      </c>
-      <c r="D4" s="11" t="inlineStr">
-        <is>
-          <t>Modalidad por confirmar</t>
+      <c r="C4" s="10" t="inlineStr">
+        <is>
+          <t>Profundización</t>
         </is>
       </c>
     </row>
@@ -1206,29 +1154,23 @@
         </is>
       </c>
       <c r="B5" s="6" t="n">
-        <v>8</v>
+        <v>15</v>
       </c>
       <c r="C5" s="6" t="n">
         <v>11</v>
       </c>
-      <c r="D5" s="6" t="n">
-        <v>7</v>
-      </c>
     </row>
     <row r="6">
-      <c r="A6" s="12" t="inlineStr">
+      <c r="A6" s="11" t="inlineStr">
         <is>
           <t>GEFEM</t>
         </is>
       </c>
-      <c r="B6" s="12" t="n">
-        <v>7</v>
-      </c>
-      <c r="C6" s="12" t="n">
+      <c r="B6" s="11" t="n">
+        <v>10</v>
+      </c>
+      <c r="C6" s="11" t="n">
         <v>9</v>
-      </c>
-      <c r="D6" s="12" t="n">
-        <v>3</v>
       </c>
     </row>
     <row r="7">
@@ -1238,124 +1180,100 @@
         </is>
       </c>
       <c r="B7" s="6" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="C7" s="6" t="n">
         <v>3</v>
       </c>
-      <c r="D7" s="6" t="n">
-        <v>1</v>
-      </c>
     </row>
     <row r="8">
-      <c r="A8" s="12" t="inlineStr">
+      <c r="A8" s="11" t="inlineStr">
         <is>
           <t>INTERNET INTELIGENTE</t>
         </is>
       </c>
-      <c r="B8" s="12" t="n">
+      <c r="B8" s="11" t="n">
         <v>2</v>
       </c>
-      <c r="C8" s="12" t="n">
+      <c r="C8" s="11" t="n">
         <v>8</v>
-      </c>
-      <c r="D8" s="12" t="n">
-        <v>0</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="6" t="inlineStr">
         <is>
+          <t>GITEM</t>
+        </is>
+      </c>
+      <c r="B9" s="6" t="n">
+        <v>5</v>
+      </c>
+      <c r="C9" s="6" t="n">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="11" t="inlineStr">
+        <is>
           <t>GICOGE</t>
         </is>
       </c>
-      <c r="B9" s="6" t="n">
+      <c r="B10" s="11" t="n">
         <v>7</v>
       </c>
-      <c r="C9" s="6" t="n">
+      <c r="C10" s="11" t="n">
         <v>2</v>
-      </c>
-      <c r="D9" s="6" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" s="12" t="inlineStr">
-        <is>
-          <t>GITEM</t>
-        </is>
-      </c>
-      <c r="B10" s="12" t="n">
-        <v>4</v>
-      </c>
-      <c r="C10" s="12" t="n">
-        <v>4</v>
-      </c>
-      <c r="D10" s="12" t="n">
-        <v>1</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="6" t="inlineStr">
         <is>
-          <t>Multimedia Interactiva y Animación Digital</t>
+          <t>GRECO</t>
         </is>
       </c>
       <c r="B11" s="6" t="n">
-        <v>3</v>
+        <v>7</v>
       </c>
       <c r="C11" s="6" t="n">
-        <v>4</v>
-      </c>
-      <c r="D11" s="6" t="n">
         <v>1</v>
       </c>
     </row>
     <row r="12">
-      <c r="A12" s="12" t="inlineStr">
-        <is>
-          <t>GRECO</t>
-        </is>
-      </c>
-      <c r="B12" s="12" t="n">
+      <c r="A12" s="11" t="inlineStr">
+        <is>
+          <t>GIIRA</t>
+        </is>
+      </c>
+      <c r="B12" s="11" t="n">
+        <v>6</v>
+      </c>
+      <c r="C12" s="11" t="n">
         <v>2</v>
-      </c>
-      <c r="C12" s="12" t="n">
-        <v>1</v>
-      </c>
-      <c r="D12" s="12" t="n">
-        <v>5</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="6" t="inlineStr">
         <is>
-          <t>GIIRA</t>
+          <t>Multimedia Interactiva y Animación Digital</t>
         </is>
       </c>
       <c r="B13" s="6" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="C13" s="6" t="n">
-        <v>2</v>
-      </c>
-      <c r="D13" s="6" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
     </row>
     <row r="14">
-      <c r="A14" s="12" t="inlineStr">
+      <c r="A14" s="11" t="inlineStr">
         <is>
           <t>GITUD</t>
         </is>
       </c>
-      <c r="B14" s="12" t="n">
+      <c r="B14" s="11" t="n">
         <v>7</v>
       </c>
-      <c r="C14" s="12" t="n">
-        <v>0</v>
-      </c>
-      <c r="D14" s="12" t="n">
+      <c r="C14" s="11" t="n">
         <v>0</v>
       </c>
     </row>
@@ -1371,24 +1289,18 @@
       <c r="C15" s="6" t="n">
         <v>0</v>
       </c>
-      <c r="D15" s="6" t="n">
-        <v>0</v>
-      </c>
     </row>
     <row r="16">
-      <c r="A16" s="12" t="inlineStr">
+      <c r="A16" s="11" t="inlineStr">
         <is>
           <t>LASER</t>
         </is>
       </c>
-      <c r="B16" s="12" t="n">
+      <c r="B16" s="11" t="n">
         <v>4</v>
       </c>
-      <c r="C16" s="12" t="n">
+      <c r="C16" s="11" t="n">
         <v>2</v>
-      </c>
-      <c r="D16" s="12" t="n">
-        <v>0</v>
       </c>
     </row>
     <row r="17">
@@ -1403,30 +1315,24 @@
       <c r="C17" s="6" t="n">
         <v>3</v>
       </c>
-      <c r="D17" s="6" t="n">
-        <v>0</v>
-      </c>
     </row>
     <row r="18">
-      <c r="A18" s="12" t="inlineStr">
+      <c r="A18" s="11" t="inlineStr">
         <is>
           <t>ITI</t>
         </is>
       </c>
-      <c r="B18" s="12" t="n">
+      <c r="B18" s="11" t="n">
         <v>3</v>
       </c>
-      <c r="C18" s="12" t="n">
-        <v>0</v>
-      </c>
-      <c r="D18" s="12" t="n">
+      <c r="C18" s="11" t="n">
         <v>0</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="6" t="inlineStr">
         <is>
-          <t>ARMOS</t>
+          <t>IAFT</t>
         </is>
       </c>
       <c r="B19" s="6" t="n">
@@ -1435,30 +1341,24 @@
       <c r="C19" s="6" t="n">
         <v>1</v>
       </c>
-      <c r="D19" s="6" t="n">
-        <v>0</v>
-      </c>
     </row>
     <row r="20">
-      <c r="A20" s="12" t="inlineStr">
+      <c r="A20" s="11" t="inlineStr">
         <is>
           <t>GICOECOL</t>
         </is>
       </c>
-      <c r="B20" s="12" t="n">
+      <c r="B20" s="11" t="n">
         <v>1</v>
       </c>
-      <c r="C20" s="12" t="n">
+      <c r="C20" s="11" t="n">
         <v>1</v>
-      </c>
-      <c r="D20" s="12" t="n">
-        <v>0</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" s="6" t="inlineStr">
         <is>
-          <t>IAFT</t>
+          <t>ARMOS</t>
         </is>
       </c>
       <c r="B21" s="6" t="n">
@@ -1467,55 +1367,43 @@
       <c r="C21" s="6" t="n">
         <v>1</v>
       </c>
-      <c r="D21" s="6" t="n">
+    </row>
+    <row r="22">
+      <c r="A22" s="11" t="inlineStr">
+        <is>
+          <t>GITEM++</t>
+        </is>
+      </c>
+      <c r="B22" s="11" t="n">
         <v>0</v>
       </c>
-    </row>
-    <row r="22">
-      <c r="A22" s="12" t="inlineStr">
-        <is>
-          <t>GITEM++</t>
-        </is>
-      </c>
-      <c r="B22" s="12" t="n">
-        <v>0</v>
-      </c>
-      <c r="C22" s="12" t="n">
+      <c r="C22" s="11" t="n">
         <v>1</v>
-      </c>
-      <c r="D22" s="12" t="n">
-        <v>0</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" s="6" t="inlineStr">
         <is>
-          <t>CEPMS</t>
+          <t>DIMSI</t>
         </is>
       </c>
       <c r="B23" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="C23" s="6" t="n">
         <v>1</v>
       </c>
-      <c r="C23" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="D23" s="6" t="n">
-        <v>0</v>
-      </c>
     </row>
     <row r="24">
-      <c r="A24" s="12" t="inlineStr">
-        <is>
-          <t>DIMSI</t>
-        </is>
-      </c>
-      <c r="B24" s="12" t="n">
-        <v>0</v>
-      </c>
-      <c r="C24" s="12" t="n">
+      <c r="A24" s="11" t="inlineStr">
+        <is>
+          <t>LASER LAMIC</t>
+        </is>
+      </c>
+      <c r="B24" s="11" t="n">
         <v>1</v>
       </c>
-      <c r="D24" s="12" t="n">
+      <c r="C24" s="11" t="n">
         <v>0</v>
       </c>
     </row>
@@ -1531,55 +1419,43 @@
       <c r="C25" s="6" t="n">
         <v>0</v>
       </c>
-      <c r="D25" s="6" t="n">
-        <v>0</v>
-      </c>
     </row>
     <row r="26">
-      <c r="A26" s="12" t="inlineStr">
-        <is>
-          <t>LASER LAMIC</t>
-        </is>
-      </c>
-      <c r="B26" s="12" t="n">
+      <c r="A26" s="11" t="inlineStr">
+        <is>
+          <t>CEPMS</t>
+        </is>
+      </c>
+      <c r="B26" s="11" t="n">
         <v>1</v>
       </c>
-      <c r="C26" s="12" t="n">
-        <v>0</v>
-      </c>
-      <c r="D26" s="12" t="n">
+      <c r="C26" s="11" t="n">
         <v>0</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" s="6" t="inlineStr">
         <is>
-          <t>Bionanotecnología</t>
+          <t>XUE</t>
         </is>
       </c>
       <c r="B27" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="C27" s="6" t="n">
         <v>1</v>
       </c>
-      <c r="C27" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="D27" s="6" t="n">
-        <v>0</v>
-      </c>
     </row>
     <row r="28">
-      <c r="A28" s="12" t="inlineStr">
+      <c r="A28" s="11" t="inlineStr">
         <is>
           <t>COMPLEX UD</t>
         </is>
       </c>
-      <c r="B28" s="12" t="n">
+      <c r="B28" s="11" t="n">
         <v>1</v>
       </c>
-      <c r="C28" s="12" t="n">
-        <v>0</v>
-      </c>
-      <c r="D28" s="12" t="n">
+      <c r="C28" s="11" t="n">
         <v>0</v>
       </c>
     </row>
@@ -1595,23 +1471,17 @@
       <c r="C29" s="6" t="n">
         <v>0</v>
       </c>
-      <c r="D29" s="6" t="n">
-        <v>0</v>
-      </c>
     </row>
     <row r="30">
-      <c r="A30" s="12" t="inlineStr">
-        <is>
-          <t>XUE</t>
-        </is>
-      </c>
-      <c r="B30" s="12" t="n">
-        <v>0</v>
-      </c>
-      <c r="C30" s="12" t="n">
+      <c r="A30" s="11" t="inlineStr">
+        <is>
+          <t>Bionanotecnología</t>
+        </is>
+      </c>
+      <c r="B30" s="11" t="n">
         <v>1</v>
       </c>
-      <c r="D30" s="12" t="n">
+      <c r="C30" s="11" t="n">
         <v>0</v>
       </c>
     </row>
@@ -1656,67 +1526,67 @@
       </c>
     </row>
     <row r="3" ht="30" customHeight="1">
-      <c r="A3" s="11" t="inlineStr">
+      <c r="A3" s="10" t="inlineStr">
         <is>
           <t>ID</t>
         </is>
       </c>
-      <c r="B3" s="11" t="inlineStr">
+      <c r="B3" s="10" t="inlineStr">
         <is>
           <t>Grupo de investigación</t>
         </is>
       </c>
-      <c r="C3" s="11" t="inlineStr">
+      <c r="C3" s="10" t="inlineStr">
         <is>
           <t>Título del trabajo de grado</t>
         </is>
       </c>
-      <c r="D3" s="11" t="inlineStr">
+      <c r="D3" s="10" t="inlineStr">
         <is>
           <t>Año</t>
         </is>
       </c>
-      <c r="E3" s="11" t="inlineStr">
+      <c r="E3" s="10" t="inlineStr">
         <is>
           <t>Modalidad</t>
         </is>
       </c>
-      <c r="F3" s="11" t="inlineStr">
+      <c r="F3" s="10" t="inlineStr">
         <is>
           <t>Director(es)</t>
         </is>
       </c>
-      <c r="G3" s="11" t="inlineStr">
+      <c r="G3" s="10" t="inlineStr">
         <is>
           <t>Estudiante(s)</t>
         </is>
       </c>
-      <c r="H3" s="11" t="inlineStr">
+      <c r="H3" s="10" t="inlineStr">
         <is>
           <t>Fecha / soporte de finalización</t>
         </is>
       </c>
-      <c r="I3" s="11" t="inlineStr">
+      <c r="I3" s="10" t="inlineStr">
         <is>
           <t>Enlace RIUD</t>
         </is>
       </c>
-      <c r="J3" s="11" t="inlineStr">
+      <c r="J3" s="10" t="inlineStr">
         <is>
           <t>Estado de sustentación</t>
         </is>
       </c>
-      <c r="K3" s="11" t="inlineStr">
+      <c r="K3" s="10" t="inlineStr">
         <is>
           <t>Tipo de trabajo</t>
         </is>
       </c>
-      <c r="L3" s="11" t="inlineStr">
+      <c r="L3" s="10" t="inlineStr">
         <is>
           <t>Nota de modalidad</t>
         </is>
       </c>
-      <c r="M3" s="11" t="inlineStr">
+      <c r="M3" s="10" t="inlineStr">
         <is>
           <t>Observación de cruce</t>
         </is>
@@ -1774,55 +1644,55 @@
       <c r="M4" s="6" t="inlineStr"/>
     </row>
     <row r="5">
-      <c r="A5" s="12" t="n">
+      <c r="A5" s="11" t="n">
         <v>5</v>
       </c>
-      <c r="B5" s="12" t="inlineStr">
+      <c r="B5" s="11" t="inlineStr">
         <is>
           <t>Multimedia Interactiva y Animación Digital</t>
         </is>
       </c>
-      <c r="C5" s="12" t="inlineStr">
+      <c r="C5" s="11" t="inlineStr">
         <is>
           <t>Modelo para la evaluación de la calidad intrínseca y dinámica de los datos abiertos sector salud en Bogotá D.C. basado en Machine Learning</t>
         </is>
       </c>
-      <c r="D5" s="12" t="n">
+      <c r="D5" s="11" t="n">
         <v>2025</v>
       </c>
-      <c r="E5" s="12" t="inlineStr">
-        <is>
-          <t>Profundización</t>
-        </is>
-      </c>
-      <c r="F5" s="12" t="inlineStr">
+      <c r="E5" s="11" t="inlineStr">
+        <is>
+          <t>Profundización</t>
+        </is>
+      </c>
+      <c r="F5" s="11" t="inlineStr">
         <is>
           <t>Paulo Alonso Gaona García</t>
         </is>
       </c>
-      <c r="G5" s="12" t="inlineStr">
+      <c r="G5" s="11" t="inlineStr">
         <is>
           <t>Alvaro Varon Capera</t>
         </is>
       </c>
-      <c r="H5" s="12" t="inlineStr">
+      <c r="H5" s="11" t="inlineStr">
         <is>
           <t>2025-02-28</t>
         </is>
       </c>
-      <c r="I5" s="12" t="n"/>
-      <c r="J5" s="12" t="inlineStr">
+      <c r="I5" s="11" t="n"/>
+      <c r="J5" s="11" t="inlineStr">
         <is>
           <t>Sustentado</t>
         </is>
       </c>
-      <c r="K5" s="12" t="inlineStr">
-        <is>
-          <t>Trabajo de profundización</t>
-        </is>
-      </c>
-      <c r="L5" s="12" t="inlineStr"/>
-      <c r="M5" s="12" t="inlineStr"/>
+      <c r="K5" s="11" t="inlineStr">
+        <is>
+          <t>Trabajo de profundización</t>
+        </is>
+      </c>
+      <c r="L5" s="11" t="inlineStr"/>
+      <c r="M5" s="11" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" s="6" t="n">
@@ -1876,56 +1746,56 @@
       <c r="M6" s="6" t="inlineStr"/>
     </row>
     <row r="7">
-      <c r="A7" s="12" t="n">
+      <c r="A7" s="11" t="n">
         <v>13</v>
       </c>
-      <c r="B7" s="12" t="inlineStr">
+      <c r="B7" s="11" t="inlineStr">
         <is>
           <t>GICOGE</t>
         </is>
       </c>
-      <c r="C7" s="12" t="inlineStr">
+      <c r="C7" s="11" t="inlineStr">
         <is>
           <t>MEDICIÓN DE LA DIFERENCIA DE FASE DE LA SEÑAL DE SALIDA DE OSCILADORES ATÓMICOS MEDIANTE COMPARACIÓN SATELITAL.</t>
         </is>
       </c>
-      <c r="D7" s="12" t="n">
+      <c r="D7" s="11" t="n">
         <v>2026</v>
       </c>
-      <c r="E7" s="12" t="inlineStr">
-        <is>
-          <t>Profundización</t>
-        </is>
-      </c>
-      <c r="F7" s="12" t="inlineStr">
+      <c r="E7" s="11" t="inlineStr">
+        <is>
+          <t>Profundización</t>
+        </is>
+      </c>
+      <c r="F7" s="11" t="inlineStr">
         <is>
           <t>Nelson Enrique Vera
 Codirector: Nelson Bahamón Córtes</t>
         </is>
       </c>
-      <c r="G7" s="12" t="inlineStr">
+      <c r="G7" s="11" t="inlineStr">
         <is>
           <t>Claudia Fernanda Rodríguez Rodríguez</t>
         </is>
       </c>
-      <c r="H7" s="12" t="inlineStr">
+      <c r="H7" s="11" t="inlineStr">
         <is>
           <t>2026-06-11 | Acta 020-2026</t>
         </is>
       </c>
-      <c r="I7" s="12" t="n"/>
-      <c r="J7" s="12" t="inlineStr">
+      <c r="I7" s="11" t="n"/>
+      <c r="J7" s="11" t="inlineStr">
         <is>
           <t>Sustentado</t>
         </is>
       </c>
-      <c r="K7" s="12" t="inlineStr">
-        <is>
-          <t>Trabajo de profundización</t>
-        </is>
-      </c>
-      <c r="L7" s="12" t="inlineStr"/>
-      <c r="M7" s="12" t="inlineStr">
+      <c r="K7" s="11" t="inlineStr">
+        <is>
+          <t>Trabajo de profundización</t>
+        </is>
+      </c>
+      <c r="L7" s="11" t="inlineStr"/>
+      <c r="M7" s="11" t="inlineStr">
         <is>
           <t>Año actualizado de 2024 a 2026 según fecha efectiva de sustentación. Título actualizado según programación de sustentaciones.</t>
         </is>
@@ -1983,55 +1853,55 @@
       <c r="M8" s="6" t="inlineStr"/>
     </row>
     <row r="9">
-      <c r="A9" s="12" t="n">
+      <c r="A9" s="11" t="n">
         <v>20</v>
       </c>
-      <c r="B9" s="12" t="inlineStr">
+      <c r="B9" s="11" t="inlineStr">
         <is>
           <t>NIDE</t>
         </is>
       </c>
-      <c r="C9" s="12" t="inlineStr">
+      <c r="C9" s="11" t="inlineStr">
         <is>
           <t>Simulador de un simulador de datos de radar metereologico de polarizacion dual para zonas ecuatoriales</t>
         </is>
       </c>
-      <c r="D9" s="12" t="n">
+      <c r="D9" s="11" t="n">
         <v>2022</v>
       </c>
-      <c r="E9" s="12" t="inlineStr">
-        <is>
-          <t>Profundización</t>
-        </is>
-      </c>
-      <c r="F9" s="12" t="inlineStr">
+      <c r="E9" s="11" t="inlineStr">
+        <is>
+          <t>Profundización</t>
+        </is>
+      </c>
+      <c r="F9" s="11" t="inlineStr">
         <is>
           <t>Ernesto Gomez Vargas, Lydia Marleny Prieto Leon</t>
         </is>
       </c>
-      <c r="G9" s="12" t="inlineStr">
+      <c r="G9" s="11" t="inlineStr">
         <is>
           <t>Gustavo Alejandro Robayo Mendez</t>
         </is>
       </c>
-      <c r="H9" s="12" t="inlineStr">
+      <c r="H9" s="11" t="inlineStr">
         <is>
           <t>2022-07-13</t>
         </is>
       </c>
-      <c r="I9" s="12" t="n"/>
-      <c r="J9" s="12" t="inlineStr">
+      <c r="I9" s="11" t="n"/>
+      <c r="J9" s="11" t="inlineStr">
         <is>
           <t>Sustentado</t>
         </is>
       </c>
-      <c r="K9" s="12" t="inlineStr">
-        <is>
-          <t>Trabajo de profundización</t>
-        </is>
-      </c>
-      <c r="L9" s="12" t="inlineStr"/>
-      <c r="M9" s="12" t="inlineStr"/>
+      <c r="K9" s="11" t="inlineStr">
+        <is>
+          <t>Trabajo de profundización</t>
+        </is>
+      </c>
+      <c r="L9" s="11" t="inlineStr"/>
+      <c r="M9" s="11" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" s="6" t="n">
@@ -2089,59 +1959,59 @@
       <c r="M10" s="6" t="inlineStr"/>
     </row>
     <row r="11">
-      <c r="A11" s="12" t="n">
+      <c r="A11" s="11" t="n">
         <v>33</v>
       </c>
-      <c r="B11" s="12" t="inlineStr">
+      <c r="B11" s="11" t="inlineStr">
         <is>
           <t>GEFEM</t>
         </is>
       </c>
-      <c r="C11" s="12" t="inlineStr">
+      <c r="C11" s="11" t="inlineStr">
         <is>
           <t>Implementación de diferentes técnicas de clasificación de imágenes satelitales multiespectrales para la identificación de coberturas y zonificación del complejo de paramo de chingaza en la jurisdicción de la corporación autónoma regional del guavio corpoguavio</t>
         </is>
       </c>
-      <c r="D11" s="12" t="n">
+      <c r="D11" s="11" t="n">
         <v>2022</v>
       </c>
-      <c r="E11" s="12" t="inlineStr">
-        <is>
-          <t>Profundización</t>
-        </is>
-      </c>
-      <c r="F11" s="12" t="inlineStr">
+      <c r="E11" s="11" t="inlineStr">
+        <is>
+          <t>Profundización</t>
+        </is>
+      </c>
+      <c r="F11" s="11" t="inlineStr">
         <is>
           <t>Rubén Javier Medina Daza</t>
         </is>
       </c>
-      <c r="G11" s="12" t="inlineStr">
+      <c r="G11" s="11" t="inlineStr">
         <is>
           <t>German David Montoya Quintero</t>
         </is>
       </c>
-      <c r="H11" s="12" t="n"/>
-      <c r="I11" s="12" t="inlineStr">
+      <c r="H11" s="11" t="n"/>
+      <c r="I11" s="11" t="inlineStr">
         <is>
           <t>https://repository.udistrital.edu.co/items/c5d54668-e454-4b9d-8cb6-3da6f1355eeb</t>
         </is>
       </c>
-      <c r="J11" s="12" t="inlineStr">
+      <c r="J11" s="11" t="inlineStr">
         <is>
           <t>Sustentado</t>
         </is>
       </c>
-      <c r="K11" s="12" t="inlineStr">
-        <is>
-          <t>Trabajo de profundización</t>
-        </is>
-      </c>
-      <c r="L11" s="12" t="inlineStr">
+      <c r="K11" s="11" t="inlineStr">
+        <is>
+          <t>Trabajo de profundización</t>
+        </is>
+      </c>
+      <c r="L11" s="11" t="inlineStr">
         <is>
           <t>Inferida por nombre (Cóndor/bases); verificar</t>
         </is>
       </c>
-      <c r="M11" s="12" t="inlineStr">
+      <c r="M11" s="11" t="inlineStr">
         <is>
           <t>Grupo GEFEM confirmado mediante la base de trabajos avalados del grupo.</t>
         </is>
@@ -2203,59 +2073,59 @@
       <c r="M12" s="6" t="inlineStr"/>
     </row>
     <row r="13">
-      <c r="A13" s="12" t="n">
+      <c r="A13" s="11" t="n">
         <v>39</v>
       </c>
-      <c r="B13" s="12" t="inlineStr">
+      <c r="B13" s="11" t="inlineStr">
         <is>
           <t>GEFEM</t>
         </is>
       </c>
-      <c r="C13" s="12" t="inlineStr">
+      <c r="C13" s="11" t="inlineStr">
         <is>
           <t>Generación e implementación de una metodología para el análisis espacial de restricciones y condicionantes a derechos de uso y propiedad de la tierra sobre predios objeto de regularización, formalización, acceso y restitución de tierras en Colombia</t>
         </is>
       </c>
-      <c r="D13" s="12" t="n">
+      <c r="D13" s="11" t="n">
         <v>2023</v>
       </c>
-      <c r="E13" s="12" t="inlineStr">
-        <is>
-          <t>Profundización</t>
-        </is>
-      </c>
-      <c r="F13" s="12" t="inlineStr">
+      <c r="E13" s="11" t="inlineStr">
+        <is>
+          <t>Profundización</t>
+        </is>
+      </c>
+      <c r="F13" s="11" t="inlineStr">
         <is>
           <t>Luis Eduardo Castillo Mendez</t>
         </is>
       </c>
-      <c r="G13" s="12" t="inlineStr">
+      <c r="G13" s="11" t="inlineStr">
         <is>
           <t>Oscar Javier Castillo Castellanos</t>
         </is>
       </c>
-      <c r="H13" s="12" t="inlineStr">
+      <c r="H13" s="11" t="inlineStr">
         <is>
           <t>Acta 031-2022</t>
         </is>
       </c>
-      <c r="I13" s="12" t="inlineStr">
+      <c r="I13" s="11" t="inlineStr">
         <is>
           <t>https://repository.udistrital.edu.co/items/b6380126-e379-4ca8-82e0-dbd2a410e7e3</t>
         </is>
       </c>
-      <c r="J13" s="12" t="inlineStr">
+      <c r="J13" s="11" t="inlineStr">
         <is>
           <t>Sustentado</t>
         </is>
       </c>
-      <c r="K13" s="12" t="inlineStr">
-        <is>
-          <t>Trabajo de profundización</t>
-        </is>
-      </c>
-      <c r="L13" s="12" t="inlineStr"/>
-      <c r="M13" s="12" t="inlineStr">
+      <c r="K13" s="11" t="inlineStr">
+        <is>
+          <t>Trabajo de profundización</t>
+        </is>
+      </c>
+      <c r="L13" s="11" t="inlineStr"/>
+      <c r="M13" s="11" t="inlineStr">
         <is>
           <t>Grupo GEFEM confirmado mediante la base de trabajos avalados del grupo.</t>
         </is>
@@ -2317,59 +2187,59 @@
       <c r="M14" s="6" t="inlineStr"/>
     </row>
     <row r="15">
-      <c r="A15" s="12" t="n">
+      <c r="A15" s="11" t="n">
         <v>44</v>
       </c>
-      <c r="B15" s="12" t="inlineStr">
+      <c r="B15" s="11" t="inlineStr">
         <is>
           <t>GEFEM</t>
         </is>
       </c>
-      <c r="C15" s="12" t="inlineStr">
+      <c r="C15" s="11" t="inlineStr">
         <is>
           <t>Metodología para la valoración de riesgos de proyectos de software en Colombia</t>
         </is>
       </c>
-      <c r="D15" s="12" t="n">
+      <c r="D15" s="11" t="n">
         <v>2024</v>
       </c>
-      <c r="E15" s="12" t="inlineStr">
-        <is>
-          <t>Profundización</t>
-        </is>
-      </c>
-      <c r="F15" s="12" t="inlineStr">
+      <c r="E15" s="11" t="inlineStr">
+        <is>
+          <t>Profundización</t>
+        </is>
+      </c>
+      <c r="F15" s="11" t="inlineStr">
         <is>
           <t>Luis Eduardo Castillo Mendez; Octavio José Salcedo Parra</t>
         </is>
       </c>
-      <c r="G15" s="12" t="inlineStr">
+      <c r="G15" s="11" t="inlineStr">
         <is>
           <t>Javier Alberto Quiroga Ruiz</t>
         </is>
       </c>
-      <c r="H15" s="12" t="inlineStr">
+      <c r="H15" s="11" t="inlineStr">
         <is>
           <t>2024-09-25</t>
         </is>
       </c>
-      <c r="I15" s="12" t="inlineStr">
+      <c r="I15" s="11" t="inlineStr">
         <is>
           <t>https://repository.udistrital.edu.co/items/8fdfe1f9-9c11-48bc-9050-bf5e901cc972</t>
         </is>
       </c>
-      <c r="J15" s="12" t="inlineStr">
+      <c r="J15" s="11" t="inlineStr">
         <is>
           <t>Sustentado</t>
         </is>
       </c>
-      <c r="K15" s="12" t="inlineStr">
-        <is>
-          <t>Trabajo de profundización</t>
-        </is>
-      </c>
-      <c r="L15" s="12" t="inlineStr"/>
-      <c r="M15" s="12" t="inlineStr">
+      <c r="K15" s="11" t="inlineStr">
+        <is>
+          <t>Trabajo de profundización</t>
+        </is>
+      </c>
+      <c r="L15" s="11" t="inlineStr"/>
+      <c r="M15" s="11" t="inlineStr">
         <is>
           <t>Diferencia entre fuentes: registro previamente asociado a INTERNET INTELIGENTE; la base remitida por GEFEM lo reporta como trabajo avalado por GEFEM.</t>
         </is>
@@ -2431,59 +2301,59 @@
       <c r="M16" s="6" t="inlineStr"/>
     </row>
     <row r="17">
-      <c r="A17" s="12" t="n">
+      <c r="A17" s="11" t="n">
         <v>46</v>
       </c>
-      <c r="B17" s="12" t="inlineStr">
+      <c r="B17" s="11" t="inlineStr">
         <is>
           <t>GEFEM</t>
         </is>
       </c>
-      <c r="C17" s="12" t="inlineStr">
+      <c r="C17" s="11" t="inlineStr">
         <is>
           <t>Metodología para la evaluación de los incendios de la vegetación en la Sierra de la Macarena utilizando técnicas de análisis de imágenes basadas en objetos geográficos y árboles de decisión</t>
         </is>
       </c>
-      <c r="D17" s="12" t="n">
+      <c r="D17" s="11" t="n">
         <v>2025</v>
       </c>
-      <c r="E17" s="12" t="inlineStr">
-        <is>
-          <t>Profundización</t>
-        </is>
-      </c>
-      <c r="F17" s="12" t="inlineStr">
+      <c r="E17" s="11" t="inlineStr">
+        <is>
+          <t>Profundización</t>
+        </is>
+      </c>
+      <c r="F17" s="11" t="inlineStr">
         <is>
           <t>Rubén Javier Medina Daza</t>
         </is>
       </c>
-      <c r="G17" s="12" t="inlineStr">
+      <c r="G17" s="11" t="inlineStr">
         <is>
           <t>Gonzalo Cabezas Martín</t>
         </is>
       </c>
-      <c r="H17" s="12" t="inlineStr">
+      <c r="H17" s="11" t="inlineStr">
         <is>
           <t>2025-10-16</t>
         </is>
       </c>
-      <c r="I17" s="12" t="inlineStr">
+      <c r="I17" s="11" t="inlineStr">
         <is>
           <t>https://repository.udistrital.edu.co/items/13ed26d1-9b1a-4eeb-9ce6-b67b095a5b29</t>
         </is>
       </c>
-      <c r="J17" s="12" t="inlineStr">
+      <c r="J17" s="11" t="inlineStr">
         <is>
           <t>Sustentado</t>
         </is>
       </c>
-      <c r="K17" s="12" t="inlineStr">
-        <is>
-          <t>Trabajo de profundización</t>
-        </is>
-      </c>
-      <c r="L17" s="12" t="inlineStr"/>
-      <c r="M17" s="12" t="inlineStr"/>
+      <c r="K17" s="11" t="inlineStr">
+        <is>
+          <t>Trabajo de profundización</t>
+        </is>
+      </c>
+      <c r="L17" s="11" t="inlineStr"/>
+      <c r="M17" s="11" t="inlineStr"/>
     </row>
     <row r="18">
       <c r="A18" s="6" t="n">
@@ -2537,55 +2407,55 @@
       <c r="M18" s="6" t="inlineStr"/>
     </row>
     <row r="19">
-      <c r="A19" s="12" t="n">
+      <c r="A19" s="11" t="n">
         <v>90</v>
       </c>
-      <c r="B19" s="12" t="inlineStr">
+      <c r="B19" s="11" t="inlineStr">
         <is>
           <t>GESETIC</t>
         </is>
       </c>
-      <c r="C19" s="12" t="inlineStr">
+      <c r="C19" s="11" t="inlineStr">
         <is>
           <t>METODOLOGÍA PARA LA PREDICCIÓN DE PROBLEMAS REFERENTES A LAS TIC EN ORGANIZACIONES DE SERVICIOS GENERALES</t>
         </is>
       </c>
-      <c r="D19" s="12" t="n">
+      <c r="D19" s="11" t="n">
         <v>2022</v>
       </c>
-      <c r="E19" s="12" t="inlineStr">
-        <is>
-          <t>Profundización</t>
-        </is>
-      </c>
-      <c r="F19" s="12" t="inlineStr">
+      <c r="E19" s="11" t="inlineStr">
+        <is>
+          <t>Profundización</t>
+        </is>
+      </c>
+      <c r="F19" s="11" t="inlineStr">
         <is>
           <t>Adriana Vega</t>
         </is>
       </c>
-      <c r="G19" s="12" t="inlineStr">
+      <c r="G19" s="11" t="inlineStr">
         <is>
           <t>PINZON CASAS CHRISTIAN JESUS</t>
         </is>
       </c>
-      <c r="H19" s="12" t="inlineStr">
+      <c r="H19" s="11" t="inlineStr">
         <is>
           <t>2022-12-12</t>
         </is>
       </c>
-      <c r="I19" s="12" t="n"/>
-      <c r="J19" s="12" t="inlineStr">
+      <c r="I19" s="11" t="n"/>
+      <c r="J19" s="11" t="inlineStr">
         <is>
           <t>Sustentado</t>
         </is>
       </c>
-      <c r="K19" s="12" t="inlineStr">
-        <is>
-          <t>Trabajo de profundización</t>
-        </is>
-      </c>
-      <c r="L19" s="12" t="inlineStr"/>
-      <c r="M19" s="12" t="inlineStr"/>
+      <c r="K19" s="11" t="inlineStr">
+        <is>
+          <t>Trabajo de profundización</t>
+        </is>
+      </c>
+      <c r="L19" s="11" t="inlineStr"/>
+      <c r="M19" s="11" t="inlineStr"/>
     </row>
     <row r="20">
       <c r="A20" s="6" t="n">
@@ -2639,55 +2509,55 @@
       <c r="M20" s="6" t="inlineStr"/>
     </row>
     <row r="21">
-      <c r="A21" s="12" t="n">
+      <c r="A21" s="11" t="n">
         <v>92</v>
       </c>
-      <c r="B21" s="12" t="inlineStr">
+      <c r="B21" s="11" t="inlineStr">
         <is>
           <t>INTERNET INTELIGENTE</t>
         </is>
       </c>
-      <c r="C21" s="12" t="inlineStr">
+      <c r="C21" s="11" t="inlineStr">
         <is>
           <t>PRONOSTICO DE CONTAMINACION POR MATERIAL PARTICULADO, MEDIANTE REDES NEIRONALES ARTIFICIALES PARA GENERAR UN SISTEMA DE ALARMAS AMBIENTALES.</t>
         </is>
       </c>
-      <c r="D21" s="12" t="n">
+      <c r="D21" s="11" t="n">
         <v>2023</v>
       </c>
-      <c r="E21" s="12" t="inlineStr">
-        <is>
-          <t>Profundización</t>
-        </is>
-      </c>
-      <c r="F21" s="12" t="inlineStr">
+      <c r="E21" s="11" t="inlineStr">
+        <is>
+          <t>Profundización</t>
+        </is>
+      </c>
+      <c r="F21" s="11" t="inlineStr">
         <is>
           <t>Octavio Jose Salcedo Parra</t>
         </is>
       </c>
-      <c r="G21" s="12" t="inlineStr">
+      <c r="G21" s="11" t="inlineStr">
         <is>
           <t>CORZO MUÑOZ MIGUEL ANGEL</t>
         </is>
       </c>
-      <c r="H21" s="12" t="inlineStr">
+      <c r="H21" s="11" t="inlineStr">
         <is>
           <t>2023-11-07</t>
         </is>
       </c>
-      <c r="I21" s="12" t="n"/>
-      <c r="J21" s="12" t="inlineStr">
+      <c r="I21" s="11" t="n"/>
+      <c r="J21" s="11" t="inlineStr">
         <is>
           <t>Sustentado</t>
         </is>
       </c>
-      <c r="K21" s="12" t="inlineStr">
-        <is>
-          <t>Trabajo de profundización</t>
-        </is>
-      </c>
-      <c r="L21" s="12" t="inlineStr"/>
-      <c r="M21" s="12" t="inlineStr"/>
+      <c r="K21" s="11" t="inlineStr">
+        <is>
+          <t>Trabajo de profundización</t>
+        </is>
+      </c>
+      <c r="L21" s="11" t="inlineStr"/>
+      <c r="M21" s="11" t="inlineStr"/>
     </row>
     <row r="22">
       <c r="A22" s="6" t="n">
@@ -2741,55 +2611,55 @@
       <c r="M22" s="6" t="inlineStr"/>
     </row>
     <row r="23">
-      <c r="A23" s="12" t="n">
+      <c r="A23" s="11" t="n">
         <v>94</v>
       </c>
-      <c r="B23" s="12" t="inlineStr">
+      <c r="B23" s="11" t="inlineStr">
         <is>
           <t>GITEM</t>
         </is>
       </c>
-      <c r="C23" s="12" t="inlineStr">
+      <c r="C23" s="11" t="inlineStr">
         <is>
           <t>Modelo semántico aplicado a la gestión de contenidos en el marco de la contratación en las empresas del estado</t>
         </is>
       </c>
-      <c r="D23" s="12" t="n">
+      <c r="D23" s="11" t="n">
         <v>2024</v>
       </c>
-      <c r="E23" s="12" t="inlineStr">
-        <is>
-          <t>Profundización</t>
-        </is>
-      </c>
-      <c r="F23" s="12" t="inlineStr">
+      <c r="E23" s="11" t="inlineStr">
+        <is>
+          <t>Profundización</t>
+        </is>
+      </c>
+      <c r="F23" s="11" t="inlineStr">
         <is>
           <t>Paulo Cesar Coronado Sanchez</t>
         </is>
       </c>
-      <c r="G23" s="12" t="inlineStr">
+      <c r="G23" s="11" t="inlineStr">
         <is>
           <t>ÉRIRA TRUJILLO WILLIAM ALBERTO</t>
         </is>
       </c>
-      <c r="H23" s="12" t="inlineStr">
+      <c r="H23" s="11" t="inlineStr">
         <is>
           <t>2024-12-02</t>
         </is>
       </c>
-      <c r="I23" s="12" t="n"/>
-      <c r="J23" s="12" t="inlineStr">
+      <c r="I23" s="11" t="n"/>
+      <c r="J23" s="11" t="inlineStr">
         <is>
           <t>Sustentado</t>
         </is>
       </c>
-      <c r="K23" s="12" t="inlineStr">
-        <is>
-          <t>Trabajo de profundización</t>
-        </is>
-      </c>
-      <c r="L23" s="12" t="inlineStr"/>
-      <c r="M23" s="12" t="inlineStr"/>
+      <c r="K23" s="11" t="inlineStr">
+        <is>
+          <t>Trabajo de profundización</t>
+        </is>
+      </c>
+      <c r="L23" s="11" t="inlineStr"/>
+      <c r="M23" s="11" t="inlineStr"/>
     </row>
     <row r="24">
       <c r="A24" s="6" t="n">
@@ -2843,55 +2713,55 @@
       <c r="M24" s="6" t="inlineStr"/>
     </row>
     <row r="25">
-      <c r="A25" s="12" t="n">
+      <c r="A25" s="11" t="n">
         <v>96</v>
       </c>
-      <c r="B25" s="12" t="inlineStr">
+      <c r="B25" s="11" t="inlineStr">
         <is>
           <t>GITEM</t>
         </is>
       </c>
-      <c r="C25" s="12" t="inlineStr">
+      <c r="C25" s="11" t="inlineStr">
         <is>
           <t>MODELO DE ARQUITECTURA CORE TRANSACCIONAL BASADA EN ARQUITECTURAS REACTIVAS Y MICROSERVICIOS PARA EL SECTOR FINANCIERO COLOMBIANO / Diseño de una solución basada en computación en la nube para el telemonitoreo de saturación de oxígeno y frecuencia cardiaca en tiempo real</t>
         </is>
       </c>
-      <c r="D25" s="12" t="n">
+      <c r="D25" s="11" t="n">
         <v>2023</v>
       </c>
-      <c r="E25" s="12" t="inlineStr">
-        <is>
-          <t>Profundización</t>
-        </is>
-      </c>
-      <c r="F25" s="12" t="inlineStr">
+      <c r="E25" s="11" t="inlineStr">
+        <is>
+          <t>Profundización</t>
+        </is>
+      </c>
+      <c r="F25" s="11" t="inlineStr">
         <is>
           <t>Lilia Edith Aparicio Pico</t>
         </is>
       </c>
-      <c r="G25" s="12" t="inlineStr">
+      <c r="G25" s="11" t="inlineStr">
         <is>
           <t>DAZA ROJAS JOHN JAIRO</t>
         </is>
       </c>
-      <c r="H25" s="12" t="inlineStr">
+      <c r="H25" s="11" t="inlineStr">
         <is>
           <t>2023-05-30</t>
         </is>
       </c>
-      <c r="I25" s="12" t="n"/>
-      <c r="J25" s="12" t="inlineStr">
+      <c r="I25" s="11" t="n"/>
+      <c r="J25" s="11" t="inlineStr">
         <is>
           <t>Sustentado</t>
         </is>
       </c>
-      <c r="K25" s="12" t="inlineStr">
-        <is>
-          <t>Trabajo de profundización</t>
-        </is>
-      </c>
-      <c r="L25" s="12" t="inlineStr"/>
-      <c r="M25" s="12" t="inlineStr"/>
+      <c r="K25" s="11" t="inlineStr">
+        <is>
+          <t>Trabajo de profundización</t>
+        </is>
+      </c>
+      <c r="L25" s="11" t="inlineStr"/>
+      <c r="M25" s="11" t="inlineStr"/>
     </row>
     <row r="26">
       <c r="A26" s="6" t="n">
@@ -2946,55 +2816,55 @@
       <c r="M26" s="6" t="inlineStr"/>
     </row>
     <row r="27">
-      <c r="A27" s="12" t="n">
+      <c r="A27" s="11" t="n">
         <v>98</v>
       </c>
-      <c r="B27" s="12" t="inlineStr">
+      <c r="B27" s="11" t="inlineStr">
         <is>
           <t>NIDE</t>
         </is>
       </c>
-      <c r="C27" s="12" t="inlineStr">
+      <c r="C27" s="11" t="inlineStr">
         <is>
           <t>MODELO DE GESTIÓN DE INFORMACIÓN ESPACIAL PARA AUTORREGULAR EL ACCESO A ESTACIONES DE TRANSMILENIO UTILIZANDO HERRAMIENTAS COLABORATIVAS</t>
         </is>
       </c>
-      <c r="D27" s="12" t="n">
+      <c r="D27" s="11" t="n">
         <v>2025</v>
       </c>
-      <c r="E27" s="12" t="inlineStr">
-        <is>
-          <t>Profundización</t>
-        </is>
-      </c>
-      <c r="F27" s="12" t="inlineStr">
+      <c r="E27" s="11" t="inlineStr">
+        <is>
+          <t>Profundización</t>
+        </is>
+      </c>
+      <c r="F27" s="11" t="inlineStr">
         <is>
           <t>Luz Angela Rocha Salamanca</t>
         </is>
       </c>
-      <c r="G27" s="12" t="inlineStr">
+      <c r="G27" s="11" t="inlineStr">
         <is>
           <t>GARCÍA GUZMÁN PEDRO PABLO</t>
         </is>
       </c>
-      <c r="H27" s="12" t="inlineStr">
+      <c r="H27" s="11" t="inlineStr">
         <is>
           <t>2025-06-17</t>
         </is>
       </c>
-      <c r="I27" s="12" t="n"/>
-      <c r="J27" s="12" t="inlineStr">
+      <c r="I27" s="11" t="n"/>
+      <c r="J27" s="11" t="inlineStr">
         <is>
           <t>Sustentado</t>
         </is>
       </c>
-      <c r="K27" s="12" t="inlineStr">
-        <is>
-          <t>Trabajo de profundización</t>
-        </is>
-      </c>
-      <c r="L27" s="12" t="inlineStr"/>
-      <c r="M27" s="12" t="inlineStr"/>
+      <c r="K27" s="11" t="inlineStr">
+        <is>
+          <t>Trabajo de profundización</t>
+        </is>
+      </c>
+      <c r="L27" s="11" t="inlineStr"/>
+      <c r="M27" s="11" t="inlineStr"/>
     </row>
     <row r="28">
       <c r="A28" s="6" t="n">
@@ -3048,55 +2918,55 @@
       <c r="M28" s="6" t="inlineStr"/>
     </row>
     <row r="29">
-      <c r="A29" s="12" t="n">
+      <c r="A29" s="11" t="n">
         <v>100</v>
       </c>
-      <c r="B29" s="12" t="inlineStr">
+      <c r="B29" s="11" t="inlineStr">
         <is>
           <t>GIIRA</t>
         </is>
       </c>
-      <c r="C29" s="12" t="inlineStr">
+      <c r="C29" s="11" t="inlineStr">
         <is>
           <t>MODELO DE SIG CON EL USO DE REALIDAD AUMENTADA PARA USUARIOS POS CON DISCAPACIDAD AUDITIVA QUE USEN LOS SERVICIOS DE SALUD</t>
         </is>
       </c>
-      <c r="D29" s="12" t="n">
+      <c r="D29" s="11" t="n">
         <v>2022</v>
       </c>
-      <c r="E29" s="12" t="inlineStr">
-        <is>
-          <t>Profundización</t>
-        </is>
-      </c>
-      <c r="F29" s="12" t="inlineStr">
+      <c r="E29" s="11" t="inlineStr">
+        <is>
+          <t>Profundización</t>
+        </is>
+      </c>
+      <c r="F29" s="11" t="inlineStr">
         <is>
           <t>Carlos Enrique Montenegro</t>
         </is>
       </c>
-      <c r="G29" s="12" t="inlineStr">
+      <c r="G29" s="11" t="inlineStr">
         <is>
           <t>MONTES LÓPEZ DIEGO FERNANDO</t>
         </is>
       </c>
-      <c r="H29" s="12" t="inlineStr">
+      <c r="H29" s="11" t="inlineStr">
         <is>
           <t>2022-08-05</t>
         </is>
       </c>
-      <c r="I29" s="12" t="n"/>
-      <c r="J29" s="12" t="inlineStr">
+      <c r="I29" s="11" t="n"/>
+      <c r="J29" s="11" t="inlineStr">
         <is>
           <t>Sustentado</t>
         </is>
       </c>
-      <c r="K29" s="12" t="inlineStr">
-        <is>
-          <t>Trabajo de profundización</t>
-        </is>
-      </c>
-      <c r="L29" s="12" t="inlineStr"/>
-      <c r="M29" s="12" t="inlineStr"/>
+      <c r="K29" s="11" t="inlineStr">
+        <is>
+          <t>Trabajo de profundización</t>
+        </is>
+      </c>
+      <c r="L29" s="11" t="inlineStr"/>
+      <c r="M29" s="11" t="inlineStr"/>
     </row>
     <row r="30">
       <c r="A30" s="6" t="n">
@@ -3151,56 +3021,56 @@
       <c r="M30" s="6" t="inlineStr"/>
     </row>
     <row r="31">
-      <c r="A31" s="12" t="n">
+      <c r="A31" s="11" t="n">
         <v>102</v>
       </c>
-      <c r="B31" s="12" t="inlineStr">
+      <c r="B31" s="11" t="inlineStr">
         <is>
           <t>INTERNET INTELIGENTE</t>
         </is>
       </c>
-      <c r="C31" s="12" t="inlineStr">
+      <c r="C31" s="11" t="inlineStr">
         <is>
           <t>PREDICCION DE ESPERANZA DE VIDA, CONSIDERANDO EL COVID-19 BAJO ALGORITMOS DE MACHINE
 LEARNING BASADOS EN DATOS EPIDEMIOLOGICOS Y PATOLOGICOS</t>
         </is>
       </c>
-      <c r="D31" s="12" t="n">
+      <c r="D31" s="11" t="n">
         <v>2025</v>
       </c>
-      <c r="E31" s="12" t="inlineStr">
-        <is>
-          <t>Profundización</t>
-        </is>
-      </c>
-      <c r="F31" s="12" t="inlineStr">
+      <c r="E31" s="11" t="inlineStr">
+        <is>
+          <t>Profundización</t>
+        </is>
+      </c>
+      <c r="F31" s="11" t="inlineStr">
         <is>
           <t>Octavio Jose Salcedo Parra</t>
         </is>
       </c>
-      <c r="G31" s="12" t="inlineStr">
+      <c r="G31" s="11" t="inlineStr">
         <is>
           <t>RODRÍGUEZ LÓPEZ JORGE LEONARDO</t>
         </is>
       </c>
-      <c r="H31" s="12" t="inlineStr">
+      <c r="H31" s="11" t="inlineStr">
         <is>
           <t>2025-03-25</t>
         </is>
       </c>
-      <c r="I31" s="12" t="n"/>
-      <c r="J31" s="12" t="inlineStr">
+      <c r="I31" s="11" t="n"/>
+      <c r="J31" s="11" t="inlineStr">
         <is>
           <t>Sustentado</t>
         </is>
       </c>
-      <c r="K31" s="12" t="inlineStr">
-        <is>
-          <t>Trabajo de profundización</t>
-        </is>
-      </c>
-      <c r="L31" s="12" t="inlineStr"/>
-      <c r="M31" s="12" t="inlineStr"/>
+      <c r="K31" s="11" t="inlineStr">
+        <is>
+          <t>Trabajo de profundización</t>
+        </is>
+      </c>
+      <c r="L31" s="11" t="inlineStr"/>
+      <c r="M31" s="11" t="inlineStr"/>
     </row>
     <row r="32">
       <c r="A32" s="6" t="n">
@@ -3254,55 +3124,55 @@
       <c r="M32" s="6" t="inlineStr"/>
     </row>
     <row r="33">
-      <c r="A33" s="12" t="n">
+      <c r="A33" s="11" t="n">
         <v>104</v>
       </c>
-      <c r="B33" s="12" t="inlineStr">
+      <c r="B33" s="11" t="inlineStr">
         <is>
           <t>NIDE</t>
         </is>
       </c>
-      <c r="C33" s="12" t="inlineStr">
+      <c r="C33" s="11" t="inlineStr">
         <is>
           <t>en la detección de malware</t>
         </is>
       </c>
-      <c r="D33" s="12" t="n">
+      <c r="D33" s="11" t="n">
         <v>2025</v>
       </c>
-      <c r="E33" s="12" t="inlineStr">
-        <is>
-          <t>Profundización</t>
-        </is>
-      </c>
-      <c r="F33" s="12" t="inlineStr">
+      <c r="E33" s="11" t="inlineStr">
+        <is>
+          <t>Profundización</t>
+        </is>
+      </c>
+      <c r="F33" s="11" t="inlineStr">
         <is>
           <t>Luz Angela Rocha Salamanca</t>
         </is>
       </c>
-      <c r="G33" s="12" t="inlineStr">
+      <c r="G33" s="11" t="inlineStr">
         <is>
           <t>MONTANO MORENO ANDRES OROSMAN</t>
         </is>
       </c>
-      <c r="H33" s="12" t="inlineStr">
+      <c r="H33" s="11" t="inlineStr">
         <is>
           <t>2025-08-22</t>
         </is>
       </c>
-      <c r="I33" s="12" t="n"/>
-      <c r="J33" s="12" t="inlineStr">
+      <c r="I33" s="11" t="n"/>
+      <c r="J33" s="11" t="inlineStr">
         <is>
           <t>Sustentado</t>
         </is>
       </c>
-      <c r="K33" s="12" t="inlineStr">
-        <is>
-          <t>Trabajo de profundización</t>
-        </is>
-      </c>
-      <c r="L33" s="12" t="inlineStr"/>
-      <c r="M33" s="12" t="inlineStr"/>
+      <c r="K33" s="11" t="inlineStr">
+        <is>
+          <t>Trabajo de profundización</t>
+        </is>
+      </c>
+      <c r="L33" s="11" t="inlineStr"/>
+      <c r="M33" s="11" t="inlineStr"/>
     </row>
     <row r="34">
       <c r="A34" s="6" t="n">
@@ -3356,55 +3226,55 @@
       <c r="M34" s="6" t="inlineStr"/>
     </row>
     <row r="35">
-      <c r="A35" s="12" t="n">
+      <c r="A35" s="11" t="n">
         <v>106</v>
       </c>
-      <c r="B35" s="12" t="inlineStr">
+      <c r="B35" s="11" t="inlineStr">
         <is>
           <t>GICOECOL</t>
         </is>
       </c>
-      <c r="C35" s="12" t="inlineStr">
+      <c r="C35" s="11" t="inlineStr">
         <is>
           <t>SISTEMA IOT PARA LA GESTIÓN DE VARIABLES DE PROCESO EN AMBIENTES DE REFRIGERACIÓN DE LA INDUSTRIA CÁRNICA</t>
         </is>
       </c>
-      <c r="D35" s="12" t="n">
+      <c r="D35" s="11" t="n">
         <v>2025</v>
       </c>
-      <c r="E35" s="12" t="inlineStr">
-        <is>
-          <t>Profundización</t>
-        </is>
-      </c>
-      <c r="F35" s="12" t="inlineStr">
+      <c r="E35" s="11" t="inlineStr">
+        <is>
+          <t>Profundización</t>
+        </is>
+      </c>
+      <c r="F35" s="11" t="inlineStr">
         <is>
           <t>Luz Andrea Rodríguez Rojas</t>
         </is>
       </c>
-      <c r="G35" s="12" t="inlineStr">
+      <c r="G35" s="11" t="inlineStr">
         <is>
           <t>TRIANA USECHE JORDAN CAMILO</t>
         </is>
       </c>
-      <c r="H35" s="12" t="inlineStr">
+      <c r="H35" s="11" t="inlineStr">
         <is>
           <t>2025-04-10</t>
         </is>
       </c>
-      <c r="I35" s="12" t="n"/>
-      <c r="J35" s="12" t="inlineStr">
+      <c r="I35" s="11" t="n"/>
+      <c r="J35" s="11" t="inlineStr">
         <is>
           <t>Sustentado</t>
         </is>
       </c>
-      <c r="K35" s="12" t="inlineStr">
-        <is>
-          <t>Trabajo de profundización</t>
-        </is>
-      </c>
-      <c r="L35" s="12" t="inlineStr"/>
-      <c r="M35" s="12" t="inlineStr"/>
+      <c r="K35" s="11" t="inlineStr">
+        <is>
+          <t>Trabajo de profundización</t>
+        </is>
+      </c>
+      <c r="L35" s="11" t="inlineStr"/>
+      <c r="M35" s="11" t="inlineStr"/>
     </row>
     <row r="36">
       <c r="A36" s="6" t="n">
@@ -3458,55 +3328,55 @@
       <c r="M36" s="6" t="inlineStr"/>
     </row>
     <row r="37">
-      <c r="A37" s="12" t="n">
+      <c r="A37" s="11" t="n">
         <v>108</v>
       </c>
-      <c r="B37" s="12" t="inlineStr">
+      <c r="B37" s="11" t="inlineStr">
         <is>
           <t>INTERNET INTELIGENTE</t>
         </is>
       </c>
-      <c r="C37" s="12" t="inlineStr">
+      <c r="C37" s="11" t="inlineStr">
         <is>
           <t>DISEÑO E IMPLEMENTACION DE UN ENTORNO IOT EN CULTIVOS DE MAIZ EN LA VEREDA DE PIEDRALARGA DEL MUNICIPIO DE CIENAGA  BOYACA</t>
         </is>
       </c>
-      <c r="D37" s="12" t="n">
+      <c r="D37" s="11" t="n">
         <v>2023</v>
       </c>
-      <c r="E37" s="12" t="inlineStr">
-        <is>
-          <t>Profundización</t>
-        </is>
-      </c>
-      <c r="F37" s="12" t="inlineStr">
+      <c r="E37" s="11" t="inlineStr">
+        <is>
+          <t>Profundización</t>
+        </is>
+      </c>
+      <c r="F37" s="11" t="inlineStr">
         <is>
           <t>Octavio Jose Salcedo Parra</t>
         </is>
       </c>
-      <c r="G37" s="12" t="inlineStr">
+      <c r="G37" s="11" t="inlineStr">
         <is>
           <t>GONZALEZ PRIETO FREDY ALEXANDER</t>
         </is>
       </c>
-      <c r="H37" s="12" t="inlineStr">
+      <c r="H37" s="11" t="inlineStr">
         <is>
           <t>2023-05-23</t>
         </is>
       </c>
-      <c r="I37" s="12" t="n"/>
-      <c r="J37" s="12" t="inlineStr">
+      <c r="I37" s="11" t="n"/>
+      <c r="J37" s="11" t="inlineStr">
         <is>
           <t>Sustentado</t>
         </is>
       </c>
-      <c r="K37" s="12" t="inlineStr">
-        <is>
-          <t>Trabajo de profundización</t>
-        </is>
-      </c>
-      <c r="L37" s="12" t="inlineStr"/>
-      <c r="M37" s="12" t="inlineStr">
+      <c r="K37" s="11" t="inlineStr">
+        <is>
+          <t>Trabajo de profundización</t>
+        </is>
+      </c>
+      <c r="L37" s="11" t="inlineStr"/>
+      <c r="M37" s="11" t="inlineStr">
         <is>
           <t>Grupo completado mediante cruce nominal del director con el directorio institucional de grupos (https://pi.udistrital.edu.co/Unidad-Ingenieria/investigacion); asociación explícita del director con INTERNET INTELIGENTE. Consulta: 2026-09-19.</t>
         </is>
@@ -3564,15 +3434,15 @@
       <c r="M38" s="6" t="inlineStr"/>
     </row>
     <row r="39">
-      <c r="A39" s="12" t="n">
+      <c r="A39" s="11" t="n">
         <v>111</v>
       </c>
-      <c r="B39" s="12" t="inlineStr">
+      <c r="B39" s="11" t="inlineStr">
         <is>
           <t>XUE</t>
         </is>
       </c>
-      <c r="C39" s="12" t="inlineStr">
+      <c r="C39" s="11" t="inlineStr">
         <is>
           <t>APOYO TÉCNICO Y ADMINISTRATIVO EN EL MARCO DE CONVENIO Y
 CONTRATO DE COOPERACIÓN INTERADMINISTRATIVO PARA REALIZAR
@@ -3580,38 +3450,38 @@
 NACIONAL DE PROTECCIÓN (UNP)</t>
         </is>
       </c>
-      <c r="D39" s="12" t="n">
+      <c r="D39" s="11" t="n">
         <v>2024</v>
       </c>
-      <c r="E39" s="12" t="inlineStr">
-        <is>
-          <t>Profundización</t>
-        </is>
-      </c>
-      <c r="F39" s="12" t="inlineStr">
+      <c r="E39" s="11" t="inlineStr">
+        <is>
+          <t>Profundización</t>
+        </is>
+      </c>
+      <c r="F39" s="11" t="inlineStr">
         <is>
           <t>Andres Escobar Diaz</t>
         </is>
       </c>
-      <c r="G39" s="12" t="n"/>
-      <c r="H39" s="12" t="inlineStr">
+      <c r="G39" s="11" t="n"/>
+      <c r="H39" s="11" t="inlineStr">
         <is>
           <t>Acta 011/2024</t>
         </is>
       </c>
-      <c r="I39" s="12" t="n"/>
-      <c r="J39" s="12" t="inlineStr">
+      <c r="I39" s="11" t="n"/>
+      <c r="J39" s="11" t="inlineStr">
         <is>
           <t>Sustentado</t>
         </is>
       </c>
-      <c r="K39" s="12" t="inlineStr">
-        <is>
-          <t>Trabajo de profundización</t>
-        </is>
-      </c>
-      <c r="L39" s="12" t="inlineStr"/>
-      <c r="M39" s="12" t="inlineStr"/>
+      <c r="K39" s="11" t="inlineStr">
+        <is>
+          <t>Trabajo de profundización</t>
+        </is>
+      </c>
+      <c r="L39" s="11" t="inlineStr"/>
+      <c r="M39" s="11" t="inlineStr"/>
     </row>
     <row r="40">
       <c r="A40" s="6" t="n">
@@ -3666,15 +3536,15 @@
       <c r="M40" s="6" t="inlineStr"/>
     </row>
     <row r="41">
-      <c r="A41" s="12" t="n">
+      <c r="A41" s="11" t="n">
         <v>118</v>
       </c>
-      <c r="B41" s="12" t="inlineStr">
+      <c r="B41" s="11" t="inlineStr">
         <is>
           <t>LASER</t>
         </is>
       </c>
-      <c r="C41" s="12" t="inlineStr">
+      <c r="C41" s="11" t="inlineStr">
         <is>
           <t>Metodología para la 
 Actualización y 
@@ -3683,46 +3553,46 @@
 Colombia</t>
         </is>
       </c>
-      <c r="D41" s="12" t="n">
+      <c r="D41" s="11" t="n">
         <v>2025</v>
       </c>
-      <c r="E41" s="12" t="inlineStr">
-        <is>
-          <t>Profundización</t>
-        </is>
-      </c>
-      <c r="F41" s="12" t="inlineStr">
+      <c r="E41" s="11" t="inlineStr">
+        <is>
+          <t>Profundización</t>
+        </is>
+      </c>
+      <c r="F41" s="11" t="inlineStr">
         <is>
           <t>Cesar Andrey Perdomo Charry</t>
         </is>
       </c>
-      <c r="G41" s="12" t="inlineStr">
+      <c r="G41" s="11" t="inlineStr">
         <is>
           <t>PUENTES PEDRAZA KEVIN JULIAN</t>
         </is>
       </c>
-      <c r="H41" s="12" t="inlineStr">
+      <c r="H41" s="11" t="inlineStr">
         <is>
           <t>Acta 002-2025</t>
         </is>
       </c>
-      <c r="I41" s="12" t="n"/>
-      <c r="J41" s="12" t="inlineStr">
+      <c r="I41" s="11" t="n"/>
+      <c r="J41" s="11" t="inlineStr">
         <is>
           <t>Sustentado</t>
         </is>
       </c>
-      <c r="K41" s="12" t="inlineStr">
+      <c r="K41" s="11" t="inlineStr">
         <is>
           <t>Pasantía</t>
         </is>
       </c>
-      <c r="L41" s="12" t="inlineStr">
+      <c r="L41" s="11" t="inlineStr">
         <is>
           <t>Pasantía (opción de grado de Profundización)</t>
         </is>
       </c>
-      <c r="M41" s="12" t="inlineStr"/>
+      <c r="M41" s="11" t="inlineStr"/>
     </row>
     <row r="42">
       <c r="A42" s="6" t="n">
@@ -3780,59 +3650,59 @@
       <c r="M42" s="6" t="inlineStr"/>
     </row>
     <row r="43">
-      <c r="A43" s="12" t="n">
+      <c r="A43" s="11" t="n">
         <v>120</v>
       </c>
-      <c r="B43" s="12" t="inlineStr">
+      <c r="B43" s="11" t="inlineStr">
         <is>
           <t>NIDE</t>
         </is>
       </c>
-      <c r="C43" s="12" t="inlineStr">
+      <c r="C43" s="11" t="inlineStr">
         <is>
           <t>AUTOMATIZACIÓN DEL PROCESO DE CONFIGURACIÓN INICIAL DE UN SITIO WEB PARA LA GESTIÓN DE SEGMENTACIONES SEMÁNTICAS MANUALES Y ELABORACIÓN DE PROPUESTA DE INVESTIGACIÓN DE UN MÉTODO INDIRECTO PARA LA DETERMINACIÓN DE ZONAS HOMOGÉNEAS FÍSICAS RURALES</t>
         </is>
       </c>
-      <c r="D43" s="12" t="n">
+      <c r="D43" s="11" t="n">
         <v>2025</v>
       </c>
-      <c r="E43" s="12" t="inlineStr">
-        <is>
-          <t>Profundización</t>
-        </is>
-      </c>
-      <c r="F43" s="12" t="inlineStr">
+      <c r="E43" s="11" t="inlineStr">
+        <is>
+          <t>Profundización</t>
+        </is>
+      </c>
+      <c r="F43" s="11" t="inlineStr">
         <is>
           <t>Jose Antonio Valero</t>
         </is>
       </c>
-      <c r="G43" s="12" t="inlineStr">
+      <c r="G43" s="11" t="inlineStr">
         <is>
           <t>ORTIZ MONCADA HAESSLER JOAN</t>
         </is>
       </c>
-      <c r="H43" s="12" t="inlineStr">
+      <c r="H43" s="11" t="inlineStr">
         <is>
           <t>Acta 003-2025</t>
         </is>
       </c>
-      <c r="I43" s="12" t="n"/>
-      <c r="J43" s="12" t="inlineStr">
+      <c r="I43" s="11" t="n"/>
+      <c r="J43" s="11" t="inlineStr">
         <is>
           <t>Sustentado</t>
         </is>
       </c>
-      <c r="K43" s="12" t="inlineStr">
+      <c r="K43" s="11" t="inlineStr">
         <is>
           <t>Pasantía</t>
         </is>
       </c>
-      <c r="L43" s="12" t="inlineStr">
+      <c r="L43" s="11" t="inlineStr">
         <is>
           <t>Pasantía (opción de grado de Profundización)</t>
         </is>
       </c>
-      <c r="M43" s="12" t="inlineStr">
+      <c r="M43" s="11" t="inlineStr">
         <is>
           <t>Carta de Aval formal del grupo NIDE para pasantía verificada en Bronze.</t>
         </is>
@@ -3894,55 +3764,55 @@
       </c>
     </row>
     <row r="45">
-      <c r="A45" s="12" t="n">
+      <c r="A45" s="11" t="n">
         <v>126</v>
       </c>
-      <c r="B45" s="12" t="inlineStr">
+      <c r="B45" s="11" t="inlineStr">
         <is>
           <t>INTERNET INTELIGENTE</t>
         </is>
       </c>
-      <c r="C45" s="12" t="inlineStr">
+      <c r="C45" s="11" t="inlineStr">
         <is>
           <t>PROTOTIPO DE SISTEMA LUMINICO PARA LA PRODUCCION CONTROLADA DE PLANTAS MEDICINALES DE LA TAXONOMIA CANNABIS SATIVA VAR. RUDERALIS UTILIZANDO ENERGIAS ALTERNATIVAS</t>
         </is>
       </c>
-      <c r="D45" s="12" t="n">
+      <c r="D45" s="11" t="n">
         <v>2026</v>
       </c>
-      <c r="E45" s="12" t="inlineStr">
-        <is>
-          <t>Profundización</t>
-        </is>
-      </c>
-      <c r="F45" s="12" t="inlineStr">
+      <c r="E45" s="11" t="inlineStr">
+        <is>
+          <t>Profundización</t>
+        </is>
+      </c>
+      <c r="F45" s="11" t="inlineStr">
         <is>
           <t>Octavio José Salcedo Parra</t>
         </is>
       </c>
-      <c r="G45" s="12" t="inlineStr">
+      <c r="G45" s="11" t="inlineStr">
         <is>
           <t>Omar Pedraza Romero</t>
         </is>
       </c>
-      <c r="H45" s="12" t="inlineStr">
+      <c r="H45" s="11" t="inlineStr">
         <is>
           <t>2026-05-13 | Acta 006 - 2026</t>
         </is>
       </c>
-      <c r="I45" s="12" t="n"/>
-      <c r="J45" s="12" t="inlineStr">
+      <c r="I45" s="11" t="n"/>
+      <c r="J45" s="11" t="inlineStr">
         <is>
           <t>Sustentado</t>
         </is>
       </c>
-      <c r="K45" s="12" t="inlineStr">
-        <is>
-          <t>Trabajo de profundización</t>
-        </is>
-      </c>
-      <c r="L45" s="12" t="inlineStr"/>
-      <c r="M45" s="12" t="inlineStr">
+      <c r="K45" s="11" t="inlineStr">
+        <is>
+          <t>Trabajo de profundización</t>
+        </is>
+      </c>
+      <c r="L45" s="11" t="inlineStr"/>
+      <c r="M45" s="11" t="inlineStr">
         <is>
           <t>Grupo completado mediante cruce nominal del director con el directorio institucional de grupos (https://pi.udistrital.edu.co/Unidad-Ingenieria/investigacion); asociación explícita del director con INTERNET INTELIGENTE. Consulta: 2026-09-19.</t>
         </is>
@@ -4004,55 +3874,55 @@
       </c>
     </row>
     <row r="47">
-      <c r="A47" s="12" t="n">
+      <c r="A47" s="11" t="n">
         <v>128</v>
       </c>
-      <c r="B47" s="12" t="inlineStr">
+      <c r="B47" s="11" t="inlineStr">
         <is>
           <t>NIDE</t>
         </is>
       </c>
-      <c r="C47" s="12" t="inlineStr">
+      <c r="C47" s="11" t="inlineStr">
         <is>
           <t>VULNERAVILIDAD TERRITORIAL A LA QUEMA DE BIOMASA EN CIUDAD BOLÍVAR, BOGOTÁ 2024</t>
         </is>
       </c>
-      <c r="D47" s="12" t="n">
+      <c r="D47" s="11" t="n">
         <v>2026</v>
       </c>
-      <c r="E47" s="12" t="inlineStr">
-        <is>
-          <t>Profundización</t>
-        </is>
-      </c>
-      <c r="F47" s="12" t="inlineStr">
+      <c r="E47" s="11" t="inlineStr">
+        <is>
+          <t>Profundización</t>
+        </is>
+      </c>
+      <c r="F47" s="11" t="inlineStr">
         <is>
           <t>Carlos Hernán Castro Ortega</t>
         </is>
       </c>
-      <c r="G47" s="12" t="inlineStr">
+      <c r="G47" s="11" t="inlineStr">
         <is>
           <t>Natalia Caita Sotaquira</t>
         </is>
       </c>
-      <c r="H47" s="12" t="inlineStr">
+      <c r="H47" s="11" t="inlineStr">
         <is>
           <t>Acta 011-2026</t>
         </is>
       </c>
-      <c r="I47" s="12" t="n"/>
-      <c r="J47" s="12" t="inlineStr">
+      <c r="I47" s="11" t="n"/>
+      <c r="J47" s="11" t="inlineStr">
         <is>
           <t>Sustentado</t>
         </is>
       </c>
-      <c r="K47" s="12" t="inlineStr">
-        <is>
-          <t>Trabajo de profundización</t>
-        </is>
-      </c>
-      <c r="L47" s="12" t="inlineStr"/>
-      <c r="M47" s="12" t="inlineStr">
+      <c r="K47" s="11" t="inlineStr">
+        <is>
+          <t>Trabajo de profundización</t>
+        </is>
+      </c>
+      <c r="L47" s="11" t="inlineStr"/>
+      <c r="M47" s="11" t="inlineStr">
         <is>
           <t>Carta de Aval y Viabilidad formal del grupo NIDE verificada en Bronze.</t>
         </is>
@@ -4114,56 +3984,56 @@
       </c>
     </row>
     <row r="49">
-      <c r="A49" s="12" t="n">
+      <c r="A49" s="11" t="n">
         <v>132</v>
       </c>
-      <c r="B49" s="12" t="inlineStr">
+      <c r="B49" s="11" t="inlineStr">
         <is>
           <t>GESETIC</t>
         </is>
       </c>
-      <c r="C49" s="12" t="inlineStr">
+      <c r="C49" s="11" t="inlineStr">
         <is>
           <t>DISEÑO E IMPLEMENTACIÓN DE UN GESTOR DE EVENTOS PARA LA RECOLECCIÓN AUTOMÁTICA DE REGISTROS DE FALLAS DE RELÉS DE PROTECCIÓN ELÉCTRICA MULTIMARCA A TRAVÉS DEL PROTOCOLO IEC 61850</t>
         </is>
       </c>
-      <c r="D49" s="12" t="n">
+      <c r="D49" s="11" t="n">
         <v>2026</v>
       </c>
-      <c r="E49" s="12" t="inlineStr">
-        <is>
-          <t>Profundización</t>
-        </is>
-      </c>
-      <c r="F49" s="12" t="inlineStr">
+      <c r="E49" s="11" t="inlineStr">
+        <is>
+          <t>Profundización</t>
+        </is>
+      </c>
+      <c r="F49" s="11" t="inlineStr">
         <is>
           <t>Álvaro Espinel Ortega 
 Codirector: Juan Carlos Carreño Pérez</t>
         </is>
       </c>
-      <c r="G49" s="12" t="inlineStr">
+      <c r="G49" s="11" t="inlineStr">
         <is>
           <t>Edwin Fernando Rincón Buitrago</t>
         </is>
       </c>
-      <c r="H49" s="12" t="inlineStr">
+      <c r="H49" s="11" t="inlineStr">
         <is>
           <t>2026-06-05 | Acta 016-2026</t>
         </is>
       </c>
-      <c r="I49" s="12" t="n"/>
-      <c r="J49" s="12" t="inlineStr">
+      <c r="I49" s="11" t="n"/>
+      <c r="J49" s="11" t="inlineStr">
         <is>
           <t>Sustentado</t>
         </is>
       </c>
-      <c r="K49" s="12" t="inlineStr">
-        <is>
-          <t>Trabajo de profundización</t>
-        </is>
-      </c>
-      <c r="L49" s="12" t="inlineStr"/>
-      <c r="M49" s="12" t="inlineStr">
+      <c r="K49" s="11" t="inlineStr">
+        <is>
+          <t>Trabajo de profundización</t>
+        </is>
+      </c>
+      <c r="L49" s="11" t="inlineStr"/>
+      <c r="M49" s="11" t="inlineStr">
         <is>
           <t>Grupo completado por coincidencia nominal consistente del director en otros registros del consolidado (GESETIC); el portal institucional se usó como catálogo de contraste. Validar con certificación del grupo si se requiere soporte individual.</t>
         </is>
@@ -4225,56 +4095,56 @@
       </c>
     </row>
     <row r="51">
-      <c r="A51" s="12" t="n">
+      <c r="A51" s="11" t="n">
         <v>137</v>
       </c>
-      <c r="B51" s="12" t="inlineStr">
+      <c r="B51" s="11" t="inlineStr">
         <is>
           <t>ARMOS</t>
         </is>
       </c>
-      <c r="C51" s="12" t="inlineStr">
+      <c r="C51" s="11" t="inlineStr">
         <is>
           <t>DISEÑO E IMPLEMENTACIÓN DE UN SISTEMA RAG (RETRIEVAL-AUGMENTED GENERATION) EN UN LLM PARA LA CONSTRUCCIÓN DE REGLAS YARA EN LA DETECCIÓN DE MALWARE</t>
         </is>
       </c>
-      <c r="D51" s="12" t="n">
+      <c r="D51" s="11" t="n">
         <v>2026</v>
       </c>
-      <c r="E51" s="12" t="inlineStr">
-        <is>
-          <t>Profundización</t>
-        </is>
-      </c>
-      <c r="F51" s="12" t="inlineStr">
+      <c r="E51" s="11" t="inlineStr">
+        <is>
+          <t>Profundización</t>
+        </is>
+      </c>
+      <c r="F51" s="11" t="inlineStr">
         <is>
           <t>Edwar Jacinto Gómez
 Codirector: Eduwin Parra</t>
         </is>
       </c>
-      <c r="G51" s="12" t="inlineStr">
+      <c r="G51" s="11" t="inlineStr">
         <is>
           <t>Cesar Ivan Quintero Garzón</t>
         </is>
       </c>
-      <c r="H51" s="12" t="inlineStr">
+      <c r="H51" s="11" t="inlineStr">
         <is>
           <t>Programada: 2026-06-05</t>
         </is>
       </c>
-      <c r="I51" s="12" t="n"/>
-      <c r="J51" s="12" t="inlineStr">
+      <c r="I51" s="11" t="n"/>
+      <c r="J51" s="11" t="inlineStr">
         <is>
           <t>Programado o radicado, no sustentado</t>
         </is>
       </c>
-      <c r="K51" s="12" t="inlineStr">
-        <is>
-          <t>Trabajo de profundización</t>
-        </is>
-      </c>
-      <c r="L51" s="12" t="inlineStr"/>
-      <c r="M51" s="12" t="inlineStr">
+      <c r="K51" s="11" t="inlineStr">
+        <is>
+          <t>Trabajo de profundización</t>
+        </is>
+      </c>
+      <c r="L51" s="11" t="inlineStr"/>
+      <c r="M51" s="11" t="inlineStr">
         <is>
           <t>Grupo completado por coincidencia nominal consistente del director en otros registros del consolidado (ARMOS); el portal institucional se usó como catálogo de contraste. Validar con certificación del grupo si se requiere soporte individual.</t>
         </is>
@@ -4336,55 +4206,55 @@
       </c>
     </row>
     <row r="53">
-      <c r="A53" s="12" t="n">
+      <c r="A53" s="11" t="n">
         <v>142</v>
       </c>
-      <c r="B53" s="12" t="inlineStr">
+      <c r="B53" s="11" t="inlineStr">
         <is>
           <t>NIDE</t>
         </is>
       </c>
-      <c r="C53" s="12" t="inlineStr">
+      <c r="C53" s="11" t="inlineStr">
         <is>
           <t>ESTIMACIÓN DE LOS VALORES DEL SUELO CON RELACIÓN A FENÓMENOS SOCIALES ALREDEDOR DE CENTRALIDADES SOCIOECONÓMICAS ESTRUCTURANTES EN BOGOTÁ, ÁREAS DE ANÁLISIS: CORABASTOS, AEROPUERTO EL DORADO, 20 DE JULIO, SANTA BÁRBARA, LOS MÁRTIRES Y 7 DE AGOSTO (2021-2023</t>
         </is>
       </c>
-      <c r="D53" s="12" t="n">
+      <c r="D53" s="11" t="n">
         <v>2026</v>
       </c>
-      <c r="E53" s="12" t="inlineStr">
-        <is>
-          <t>Profundización</t>
-        </is>
-      </c>
-      <c r="F53" s="12" t="inlineStr">
+      <c r="E53" s="11" t="inlineStr">
+        <is>
+          <t>Profundización</t>
+        </is>
+      </c>
+      <c r="F53" s="11" t="inlineStr">
         <is>
           <t>Hector Javier Fuentes López</t>
         </is>
       </c>
-      <c r="G53" s="12" t="inlineStr">
+      <c r="G53" s="11" t="inlineStr">
         <is>
           <t>Rusby Vanessa Castro Alfere</t>
         </is>
       </c>
-      <c r="H53" s="12" t="inlineStr">
+      <c r="H53" s="11" t="inlineStr">
         <is>
           <t>Programada: 2026-08-28</t>
         </is>
       </c>
-      <c r="I53" s="12" t="n"/>
-      <c r="J53" s="12" t="inlineStr">
+      <c r="I53" s="11" t="n"/>
+      <c r="J53" s="11" t="inlineStr">
         <is>
           <t>Programado o radicado, no sustentado</t>
         </is>
       </c>
-      <c r="K53" s="12" t="inlineStr">
-        <is>
-          <t>Trabajo de profundización</t>
-        </is>
-      </c>
-      <c r="L53" s="12" t="inlineStr"/>
-      <c r="M53" s="12" t="inlineStr">
+      <c r="K53" s="11" t="inlineStr">
+        <is>
+          <t>Trabajo de profundización</t>
+        </is>
+      </c>
+      <c r="L53" s="11" t="inlineStr"/>
+      <c r="M53" s="11" t="inlineStr">
         <is>
           <t>Grupo completado por coincidencia nominal consistente del director en otros registros del consolidado (NIDE); el portal institucional se usó como catálogo de contraste. Validar con certificación del grupo si se requiere soporte individual.</t>
         </is>
@@ -4446,55 +4316,55 @@
       </c>
     </row>
     <row r="55">
-      <c r="A55" s="12" t="n">
+      <c r="A55" s="11" t="n">
         <v>144</v>
       </c>
-      <c r="B55" s="12" t="inlineStr">
+      <c r="B55" s="11" t="inlineStr">
         <is>
           <t>NIDE</t>
         </is>
       </c>
-      <c r="C55" s="12" t="inlineStr">
+      <c r="C55" s="11" t="inlineStr">
         <is>
           <t>SELECCIÓN DE PROVEEDORES DE TRANSPORTE INTERNACIONAL CON ORIGEN O DESTINO COLOMBIA MEDIANTE ALGORITMOS DE INTELIGENCIA ARTIFICIA</t>
         </is>
       </c>
-      <c r="D55" s="12" t="n">
+      <c r="D55" s="11" t="n">
         <v>2026</v>
       </c>
-      <c r="E55" s="12" t="inlineStr">
-        <is>
-          <t>Profundización</t>
-        </is>
-      </c>
-      <c r="F55" s="12" t="inlineStr">
+      <c r="E55" s="11" t="inlineStr">
+        <is>
+          <t>Profundización</t>
+        </is>
+      </c>
+      <c r="F55" s="11" t="inlineStr">
         <is>
           <t>Álvaro Enrique Ortíz Dávila</t>
         </is>
       </c>
-      <c r="G55" s="12" t="inlineStr">
+      <c r="G55" s="11" t="inlineStr">
         <is>
           <t>Mayer Santiago Beltrán Romero</t>
         </is>
       </c>
-      <c r="H55" s="12" t="inlineStr">
+      <c r="H55" s="11" t="inlineStr">
         <is>
           <t>Programada: 2026-08-28</t>
         </is>
       </c>
-      <c r="I55" s="12" t="n"/>
-      <c r="J55" s="12" t="inlineStr">
+      <c r="I55" s="11" t="n"/>
+      <c r="J55" s="11" t="inlineStr">
         <is>
           <t>Programado o radicado, no sustentado</t>
         </is>
       </c>
-      <c r="K55" s="12" t="inlineStr">
-        <is>
-          <t>Trabajo de profundización</t>
-        </is>
-      </c>
-      <c r="L55" s="12" t="inlineStr"/>
-      <c r="M55" s="12" t="inlineStr">
+      <c r="K55" s="11" t="inlineStr">
+        <is>
+          <t>Trabajo de profundización</t>
+        </is>
+      </c>
+      <c r="L55" s="11" t="inlineStr"/>
+      <c r="M55" s="11" t="inlineStr">
         <is>
           <t>Grupo completado por coincidencia nominal consistente del director en otros registros del consolidado (NIDE); el portal institucional se usó como catálogo de contraste. Validar con certificación del grupo si se requiere soporte individual.</t>
         </is>
@@ -4556,55 +4426,55 @@
       </c>
     </row>
     <row r="57">
-      <c r="A57" s="12" t="n">
+      <c r="A57" s="11" t="n">
         <v>146</v>
       </c>
-      <c r="B57" s="12" t="inlineStr">
+      <c r="B57" s="11" t="inlineStr">
         <is>
           <t>LIDER</t>
         </is>
       </c>
-      <c r="C57" s="12" t="inlineStr">
+      <c r="C57" s="11" t="inlineStr">
         <is>
           <t>MODELO DE REPUTACIÓN BASADO EN BLOCKCHAIN E IDENTIDAD DIGITAL AUTO-SOBERANA APLICADO AL PROCESO DE EVALUACIÓN DOCENTE</t>
         </is>
       </c>
-      <c r="D57" s="12" t="n">
+      <c r="D57" s="11" t="n">
         <v>2026</v>
       </c>
-      <c r="E57" s="12" t="inlineStr">
-        <is>
-          <t>Profundización</t>
-        </is>
-      </c>
-      <c r="F57" s="12" t="inlineStr">
+      <c r="E57" s="11" t="inlineStr">
+        <is>
+          <t>Profundización</t>
+        </is>
+      </c>
+      <c r="F57" s="11" t="inlineStr">
         <is>
           <t>Roberto A. Pava Díaz Ph.D</t>
         </is>
       </c>
-      <c r="G57" s="12" t="inlineStr">
+      <c r="G57" s="11" t="inlineStr">
         <is>
           <t>Diego Fernando Zapata Muñoz</t>
         </is>
       </c>
-      <c r="H57" s="12" t="inlineStr">
+      <c r="H57" s="11" t="inlineStr">
         <is>
           <t>Aval del grupo: 2026</t>
         </is>
       </c>
-      <c r="I57" s="12" t="n"/>
-      <c r="J57" s="12" t="inlineStr">
+      <c r="I57" s="11" t="n"/>
+      <c r="J57" s="11" t="inlineStr">
         <is>
           <t>Avalado por el grupo, no sustentado</t>
         </is>
       </c>
-      <c r="K57" s="12" t="inlineStr">
-        <is>
-          <t>Trabajo de profundización</t>
-        </is>
-      </c>
-      <c r="L57" s="12" t="inlineStr"/>
-      <c r="M57" s="12" t="inlineStr">
+      <c r="K57" s="11" t="inlineStr">
+        <is>
+          <t>Trabajo de profundización</t>
+        </is>
+      </c>
+      <c r="L57" s="11" t="inlineStr"/>
+      <c r="M57" s="11" t="inlineStr">
         <is>
           <t>Aval del grupo reportado en 2026; sustentación no verificada en las fuentes disponibles.</t>
         </is>
@@ -4706,67 +4576,67 @@
       </c>
     </row>
     <row r="3" ht="30" customHeight="1">
-      <c r="A3" s="11" t="inlineStr">
+      <c r="A3" s="10" t="inlineStr">
         <is>
           <t>ID</t>
         </is>
       </c>
-      <c r="B3" s="11" t="inlineStr">
+      <c r="B3" s="10" t="inlineStr">
         <is>
           <t>Grupo de investigación</t>
         </is>
       </c>
-      <c r="C3" s="11" t="inlineStr">
+      <c r="C3" s="10" t="inlineStr">
         <is>
           <t>Título del trabajo de grado</t>
         </is>
       </c>
-      <c r="D3" s="11" t="inlineStr">
+      <c r="D3" s="10" t="inlineStr">
         <is>
           <t>Año</t>
         </is>
       </c>
-      <c r="E3" s="11" t="inlineStr">
+      <c r="E3" s="10" t="inlineStr">
         <is>
           <t>Modalidad</t>
         </is>
       </c>
-      <c r="F3" s="11" t="inlineStr">
+      <c r="F3" s="10" t="inlineStr">
         <is>
           <t>Director(es)</t>
         </is>
       </c>
-      <c r="G3" s="11" t="inlineStr">
+      <c r="G3" s="10" t="inlineStr">
         <is>
           <t>Estudiante(s)</t>
         </is>
       </c>
-      <c r="H3" s="11" t="inlineStr">
+      <c r="H3" s="10" t="inlineStr">
         <is>
           <t>Fecha / soporte de finalización</t>
         </is>
       </c>
-      <c r="I3" s="11" t="inlineStr">
+      <c r="I3" s="10" t="inlineStr">
         <is>
           <t>Enlace RIUD</t>
         </is>
       </c>
-      <c r="J3" s="11" t="inlineStr">
+      <c r="J3" s="10" t="inlineStr">
         <is>
           <t>Estado de sustentación</t>
         </is>
       </c>
-      <c r="K3" s="11" t="inlineStr">
+      <c r="K3" s="10" t="inlineStr">
         <is>
           <t>Tipo de trabajo</t>
         </is>
       </c>
-      <c r="L3" s="11" t="inlineStr">
+      <c r="L3" s="10" t="inlineStr">
         <is>
           <t>Nota de modalidad</t>
         </is>
       </c>
-      <c r="M3" s="11" t="inlineStr">
+      <c r="M3" s="10" t="inlineStr">
         <is>
           <t>Observación de cruce</t>
         </is>
@@ -4829,55 +4699,55 @@
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="12" t="n">
+      <c r="A5" s="11" t="n">
         <v>141</v>
       </c>
-      <c r="B5" s="12" t="inlineStr">
+      <c r="B5" s="11" t="inlineStr">
         <is>
           <t>GITEM++</t>
         </is>
       </c>
-      <c r="C5" s="12" t="inlineStr">
+      <c r="C5" s="11" t="inlineStr">
         <is>
           <t>EXPLORACIÓN METODOLÓGICA MULTIVARIADA APLICADA A SEIS REGISTROS POBLACIONALES DE CÁNCER EN COLOMBIA</t>
         </is>
       </c>
-      <c r="D5" s="12" t="n">
+      <c r="D5" s="11" t="n">
         <v>2026</v>
       </c>
-      <c r="E5" s="12" t="inlineStr">
-        <is>
-          <t>Profundización</t>
-        </is>
-      </c>
-      <c r="F5" s="12" t="inlineStr">
+      <c r="E5" s="11" t="inlineStr">
+        <is>
+          <t>Profundización</t>
+        </is>
+      </c>
+      <c r="F5" s="11" t="inlineStr">
         <is>
           <t>Leonardo Plazas Nossa</t>
         </is>
       </c>
-      <c r="G5" s="12" t="inlineStr">
+      <c r="G5" s="11" t="inlineStr">
         <is>
           <t>Jhonatan González Salguero</t>
         </is>
       </c>
-      <c r="H5" s="12" t="inlineStr">
+      <c r="H5" s="11" t="inlineStr">
         <is>
           <t>Programada: 2026-08-28</t>
         </is>
       </c>
-      <c r="I5" s="12" t="n"/>
-      <c r="J5" s="12" t="inlineStr">
+      <c r="I5" s="11" t="n"/>
+      <c r="J5" s="11" t="inlineStr">
         <is>
           <t>Programado o radicado, no sustentado</t>
         </is>
       </c>
-      <c r="K5" s="12" t="inlineStr">
-        <is>
-          <t>Trabajo de profundización</t>
-        </is>
-      </c>
-      <c r="L5" s="12" t="inlineStr"/>
-      <c r="M5" s="12" t="inlineStr">
+      <c r="K5" s="11" t="inlineStr">
+        <is>
+          <t>Trabajo de profundización</t>
+        </is>
+      </c>
+      <c r="L5" s="11" t="inlineStr"/>
+      <c r="M5" s="11" t="inlineStr">
         <is>
           <t>Radicación de anteproyecto con solicitud expresa de remisión a GITEM++ verificada en Bronze.</t>
         </is>
@@ -4939,55 +4809,55 @@
       </c>
     </row>
     <row r="7">
-      <c r="A7" s="12" t="n">
+      <c r="A7" s="11" t="n">
         <v>143</v>
       </c>
-      <c r="B7" s="12" t="inlineStr">
+      <c r="B7" s="11" t="inlineStr">
         <is>
           <t>NIDE</t>
         </is>
       </c>
-      <c r="C7" s="12" t="inlineStr">
+      <c r="C7" s="11" t="inlineStr">
         <is>
           <t>MODELO DE PREDICCIÓN DE DESLIZAMIENTOS DE TIERRA A PARTIR DE LA IMPLEMENTACIÓN DE MÉTODOS DE APRENDIZAJE DE MÁQUINA</t>
         </is>
       </c>
-      <c r="D7" s="12" t="n">
+      <c r="D7" s="11" t="n">
         <v>2026</v>
       </c>
-      <c r="E7" s="12" t="inlineStr">
-        <is>
-          <t>Profundización</t>
-        </is>
-      </c>
-      <c r="F7" s="12" t="inlineStr">
+      <c r="E7" s="11" t="inlineStr">
+        <is>
+          <t>Profundización</t>
+        </is>
+      </c>
+      <c r="F7" s="11" t="inlineStr">
         <is>
           <t>Álvaro Enrique Ortíz Dávila</t>
         </is>
       </c>
-      <c r="G7" s="12" t="inlineStr">
+      <c r="G7" s="11" t="inlineStr">
         <is>
           <t>Lina Paola García Malagón</t>
         </is>
       </c>
-      <c r="H7" s="12" t="inlineStr">
+      <c r="H7" s="11" t="inlineStr">
         <is>
           <t>Programada: 2026-08-28</t>
         </is>
       </c>
-      <c r="I7" s="12" t="n"/>
-      <c r="J7" s="12" t="inlineStr">
+      <c r="I7" s="11" t="n"/>
+      <c r="J7" s="11" t="inlineStr">
         <is>
           <t>Programado o radicado, no sustentado</t>
         </is>
       </c>
-      <c r="K7" s="12" t="inlineStr">
-        <is>
-          <t>Trabajo de profundización</t>
-        </is>
-      </c>
-      <c r="L7" s="12" t="inlineStr"/>
-      <c r="M7" s="12" t="inlineStr">
+      <c r="K7" s="11" t="inlineStr">
+        <is>
+          <t>Trabajo de profundización</t>
+        </is>
+      </c>
+      <c r="L7" s="11" t="inlineStr"/>
+      <c r="M7" s="11" t="inlineStr">
         <is>
           <t>Grupo completado por coincidencia nominal consistente del director en otros registros del consolidado (NIDE); el portal institucional se usó como catálogo de contraste. Validar con certificación del grupo si se requiere soporte individual.</t>
         </is>
@@ -5049,55 +4919,55 @@
       </c>
     </row>
     <row r="9">
-      <c r="A9" s="12" t="n">
+      <c r="A9" s="11" t="n">
         <v>145</v>
       </c>
-      <c r="B9" s="12" t="inlineStr">
+      <c r="B9" s="11" t="inlineStr">
         <is>
           <t>NIDE</t>
         </is>
       </c>
-      <c r="C9" s="12" t="inlineStr">
+      <c r="C9" s="11" t="inlineStr">
         <is>
           <t>DETERMINACIÓN DE UBICACIONES DE CÁMARAS DE SEGURIDAD EN ZONAS URBANAS MEDIANTE GEMELOS DIGITALES</t>
         </is>
       </c>
-      <c r="D9" s="12" t="n">
+      <c r="D9" s="11" t="n">
         <v>2026</v>
       </c>
-      <c r="E9" s="12" t="inlineStr">
-        <is>
-          <t>Profundización</t>
-        </is>
-      </c>
-      <c r="F9" s="12" t="inlineStr">
+      <c r="E9" s="11" t="inlineStr">
+        <is>
+          <t>Profundización</t>
+        </is>
+      </c>
+      <c r="F9" s="11" t="inlineStr">
         <is>
           <t>Álvaro Enrique Ortíz Dávila</t>
         </is>
       </c>
-      <c r="G9" s="12" t="inlineStr">
+      <c r="G9" s="11" t="inlineStr">
         <is>
           <t>Christian Yesid Galindo Cano</t>
         </is>
       </c>
-      <c r="H9" s="12" t="inlineStr">
+      <c r="H9" s="11" t="inlineStr">
         <is>
           <t>Programada: 2026-09-03</t>
         </is>
       </c>
-      <c r="I9" s="12" t="n"/>
-      <c r="J9" s="12" t="inlineStr">
+      <c r="I9" s="11" t="n"/>
+      <c r="J9" s="11" t="inlineStr">
         <is>
           <t>Programado o radicado, no sustentado</t>
         </is>
       </c>
-      <c r="K9" s="12" t="inlineStr">
-        <is>
-          <t>Trabajo de profundización</t>
-        </is>
-      </c>
-      <c r="L9" s="12" t="inlineStr"/>
-      <c r="M9" s="12" t="inlineStr">
+      <c r="K9" s="11" t="inlineStr">
+        <is>
+          <t>Trabajo de profundización</t>
+        </is>
+      </c>
+      <c r="L9" s="11" t="inlineStr"/>
+      <c r="M9" s="11" t="inlineStr">
         <is>
           <t>Grupo completado por coincidencia nominal consistente del director en otros registros del consolidado (NIDE); el portal institucional se usó como catálogo de contraste. Validar con certificación del grupo si se requiere soporte individual.</t>
         </is>
@@ -5159,55 +5029,55 @@
       </c>
     </row>
     <row r="11">
-      <c r="A11" s="12" t="n">
+      <c r="A11" s="11" t="n">
         <v>147</v>
       </c>
-      <c r="B11" s="12" t="inlineStr">
+      <c r="B11" s="11" t="inlineStr">
         <is>
           <t>LIDER</t>
         </is>
       </c>
-      <c r="C11" s="12" t="inlineStr">
+      <c r="C11" s="11" t="inlineStr">
         <is>
           <t>Diseño de un Modelo participativo basado en Sistemas de Información Geográfica (SIG) para la toma de decisiones en la zonificación ambiental de la Zona de Reserva Campesina Santuario</t>
         </is>
       </c>
-      <c r="D11" s="12" t="n">
+      <c r="D11" s="11" t="n">
         <v>2026</v>
       </c>
-      <c r="E11" s="12" t="inlineStr">
-        <is>
-          <t>Profundización</t>
-        </is>
-      </c>
-      <c r="F11" s="12" t="inlineStr">
+      <c r="E11" s="11" t="inlineStr">
+        <is>
+          <t>Profundización</t>
+        </is>
+      </c>
+      <c r="F11" s="11" t="inlineStr">
         <is>
           <t>Roberto Ferro Escobar / Edgar Aguirre Buenaventura</t>
         </is>
       </c>
-      <c r="G11" s="12" t="inlineStr">
+      <c r="G11" s="11" t="inlineStr">
         <is>
           <t>Cristian Daniel Camacho Hilarión</t>
         </is>
       </c>
-      <c r="H11" s="12" t="inlineStr">
+      <c r="H11" s="11" t="inlineStr">
         <is>
           <t>Aval del grupo: 2026</t>
         </is>
       </c>
-      <c r="I11" s="12" t="n"/>
-      <c r="J11" s="12" t="inlineStr">
+      <c r="I11" s="11" t="n"/>
+      <c r="J11" s="11" t="inlineStr">
         <is>
           <t>Avalado por el grupo, no sustentado</t>
         </is>
       </c>
-      <c r="K11" s="12" t="inlineStr">
-        <is>
-          <t>Trabajo de profundización</t>
-        </is>
-      </c>
-      <c r="L11" s="12" t="inlineStr"/>
-      <c r="M11" s="12" t="inlineStr">
+      <c r="K11" s="11" t="inlineStr">
+        <is>
+          <t>Trabajo de profundización</t>
+        </is>
+      </c>
+      <c r="L11" s="11" t="inlineStr"/>
+      <c r="M11" s="11" t="inlineStr">
         <is>
           <t>Aval del grupo reportado en 2026; sustentación no verificada en las fuentes disponibles.</t>
         </is>
@@ -5223,890 +5093,6 @@
 </file>
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
-  </sheetPr>
-  <dimension ref="A1:M23"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <cols>
-    <col width="6" customWidth="1" min="1" max="1"/>
-    <col width="22" customWidth="1" min="2" max="2"/>
-    <col width="60" customWidth="1" min="3" max="3"/>
-    <col width="7" customWidth="1" min="4" max="4"/>
-    <col width="14" customWidth="1" min="5" max="5"/>
-    <col width="28" customWidth="1" min="6" max="6"/>
-    <col width="28" customWidth="1" min="7" max="7"/>
-    <col width="18" customWidth="1" min="8" max="8"/>
-    <col width="30" customWidth="1" min="9" max="9"/>
-    <col width="22" customWidth="1" min="10" max="10"/>
-    <col width="22" customWidth="1" min="11" max="11"/>
-    <col width="34" customWidth="1" min="12" max="12"/>
-    <col width="50" customWidth="1" min="13" max="13"/>
-  </cols>
-  <sheetData>
-    <row r="1" ht="24" customHeight="1">
-      <c r="A1" s="1" t="inlineStr">
-        <is>
-          <t>Casos sin modalidad registrada en las fuentes</t>
-        </is>
-      </c>
-    </row>
-    <row r="2" ht="16" customHeight="1">
-      <c r="A2" s="2" t="inlineStr">
-        <is>
-          <t>Confirmar la modalidad antes de publicar.</t>
-        </is>
-      </c>
-    </row>
-    <row r="4" ht="30" customHeight="1">
-      <c r="A4" s="11" t="inlineStr">
-        <is>
-          <t>ID</t>
-        </is>
-      </c>
-      <c r="B4" s="11" t="inlineStr">
-        <is>
-          <t>Grupo de investigación</t>
-        </is>
-      </c>
-      <c r="C4" s="11" t="inlineStr">
-        <is>
-          <t>Título del trabajo de grado</t>
-        </is>
-      </c>
-      <c r="D4" s="11" t="inlineStr">
-        <is>
-          <t>Año</t>
-        </is>
-      </c>
-      <c r="E4" s="11" t="inlineStr">
-        <is>
-          <t>Modalidad</t>
-        </is>
-      </c>
-      <c r="F4" s="11" t="inlineStr">
-        <is>
-          <t>Director(es)</t>
-        </is>
-      </c>
-      <c r="G4" s="11" t="inlineStr">
-        <is>
-          <t>Estudiante(s)</t>
-        </is>
-      </c>
-      <c r="H4" s="11" t="inlineStr">
-        <is>
-          <t>Fecha / soporte de finalización</t>
-        </is>
-      </c>
-      <c r="I4" s="11" t="inlineStr">
-        <is>
-          <t>Enlace RIUD</t>
-        </is>
-      </c>
-      <c r="J4" s="11" t="inlineStr">
-        <is>
-          <t>Estado de sustentación</t>
-        </is>
-      </c>
-      <c r="K4" s="11" t="inlineStr">
-        <is>
-          <t>Tipo de trabajo</t>
-        </is>
-      </c>
-      <c r="L4" s="11" t="inlineStr">
-        <is>
-          <t>Nota de modalidad</t>
-        </is>
-      </c>
-      <c r="M4" s="11" t="inlineStr">
-        <is>
-          <t>Observación de cruce</t>
-        </is>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" s="6" t="n">
-        <v>4</v>
-      </c>
-      <c r="B5" s="6" t="inlineStr">
-        <is>
-          <t>Multimedia Interactiva y Animación Digital</t>
-        </is>
-      </c>
-      <c r="C5" s="6" t="inlineStr">
-        <is>
-          <t>Modelo de evaluación crediticio basado en principios de un ecosistema digital bancario mediante estrategias de Business Intelligence y mecanismos de reputación en el sector de industria de turismo de las PYMES colombianas</t>
-        </is>
-      </c>
-      <c r="D5" s="6" t="n">
-        <v>2024</v>
-      </c>
-      <c r="E5" s="6" t="n"/>
-      <c r="F5" s="6" t="inlineStr">
-        <is>
-          <t>Paulo Alonso Gaona García</t>
-        </is>
-      </c>
-      <c r="G5" s="6" t="inlineStr">
-        <is>
-          <t>William Stiven Garces Rodriguez</t>
-        </is>
-      </c>
-      <c r="H5" s="6" t="n"/>
-      <c r="I5" s="6" t="n"/>
-      <c r="J5" s="6" t="inlineStr">
-        <is>
-          <t>Sustentado</t>
-        </is>
-      </c>
-      <c r="K5" s="6" t="n"/>
-      <c r="L5" s="6" t="inlineStr"/>
-      <c r="M5" s="6" t="inlineStr"/>
-    </row>
-    <row r="6">
-      <c r="A6" s="12" t="n">
-        <v>11</v>
-      </c>
-      <c r="B6" s="12" t="inlineStr">
-        <is>
-          <t>GIIRA</t>
-        </is>
-      </c>
-      <c r="C6" s="12" t="inlineStr">
-        <is>
-          <t>Diseño de una aplicación móvil para el traslado prehospitalario de víctimas de accidentes de tránsito en la ciudad de neiva</t>
-        </is>
-      </c>
-      <c r="D6" s="12" t="n">
-        <v>2026</v>
-      </c>
-      <c r="E6" s="12" t="n"/>
-      <c r="F6" s="12" t="inlineStr">
-        <is>
-          <t>Paulo Alonso Gaona García</t>
-        </is>
-      </c>
-      <c r="G6" s="12" t="inlineStr">
-        <is>
-          <t>Juan Gabriel Carvajal Vega</t>
-        </is>
-      </c>
-      <c r="H6" s="12" t="n"/>
-      <c r="I6" s="12" t="n"/>
-      <c r="J6" s="12" t="inlineStr">
-        <is>
-          <t>Sustentado</t>
-        </is>
-      </c>
-      <c r="K6" s="12" t="n"/>
-      <c r="L6" s="12" t="inlineStr"/>
-      <c r="M6" s="12" t="inlineStr"/>
-    </row>
-    <row r="7">
-      <c r="A7" s="6" t="n">
-        <v>19</v>
-      </c>
-      <c r="B7" s="6" t="inlineStr">
-        <is>
-          <t>NIDE</t>
-        </is>
-      </c>
-      <c r="C7" s="6" t="inlineStr">
-        <is>
-          <t>Modelo Cox Log-Gaussiano de los Eventos Sísmicos en Colombia Utilizando un Enfoque Bayesiano Alimentado de una Red Neuronal Artificial</t>
-        </is>
-      </c>
-      <c r="D7" s="6" t="n">
-        <v>2022</v>
-      </c>
-      <c r="E7" s="6" t="n"/>
-      <c r="F7" s="6" t="inlineStr">
-        <is>
-          <t>Carlos Eduardo Melo Martinez</t>
-        </is>
-      </c>
-      <c r="G7" s="6" t="n"/>
-      <c r="H7" s="6" t="n"/>
-      <c r="I7" s="6" t="n"/>
-      <c r="J7" s="6" t="inlineStr">
-        <is>
-          <t>Sustentado</t>
-        </is>
-      </c>
-      <c r="K7" s="6" t="n"/>
-      <c r="L7" s="6" t="inlineStr"/>
-      <c r="M7" s="6" t="inlineStr"/>
-    </row>
-    <row r="8">
-      <c r="A8" s="12" t="n">
-        <v>21</v>
-      </c>
-      <c r="B8" s="12" t="inlineStr">
-        <is>
-          <t>NIDE</t>
-        </is>
-      </c>
-      <c r="C8" s="12" t="inlineStr">
-        <is>
-          <t>Un modelo de regresión logística para el estudio de la relocalización industrial en Colombia del periodo 2005 - 2015</t>
-        </is>
-      </c>
-      <c r="D8" s="12" t="n">
-        <v>2023</v>
-      </c>
-      <c r="E8" s="12" t="n"/>
-      <c r="F8" s="12" t="inlineStr">
-        <is>
-          <t>Hector Javier Fuentes Lopez</t>
-        </is>
-      </c>
-      <c r="G8" s="12" t="inlineStr">
-        <is>
-          <t>Andres David Mesa Ospina</t>
-        </is>
-      </c>
-      <c r="H8" s="12" t="n"/>
-      <c r="I8" s="12" t="n"/>
-      <c r="J8" s="12" t="inlineStr">
-        <is>
-          <t>Sustentado</t>
-        </is>
-      </c>
-      <c r="K8" s="12" t="n"/>
-      <c r="L8" s="12" t="inlineStr"/>
-      <c r="M8" s="12" t="inlineStr"/>
-    </row>
-    <row r="9">
-      <c r="A9" s="6" t="n">
-        <v>23</v>
-      </c>
-      <c r="B9" s="6" t="inlineStr">
-        <is>
-          <t>NIDE</t>
-        </is>
-      </c>
-      <c r="C9" s="6" t="inlineStr">
-        <is>
-          <t>Análisis polarimétrico a través de "sar polarimetric target analysis" como apoyo para obtener coberturas de la tierra con la metodología corine land cover</t>
-        </is>
-      </c>
-      <c r="D9" s="6" t="n">
-        <v>2022</v>
-      </c>
-      <c r="E9" s="6" t="n"/>
-      <c r="F9" s="6" t="inlineStr">
-        <is>
-          <t>Jose Luis Herrera Escorcia</t>
-        </is>
-      </c>
-      <c r="G9" s="6" t="inlineStr">
-        <is>
-          <t>Juan Carlos Parra Garzon</t>
-        </is>
-      </c>
-      <c r="H9" s="6" t="n"/>
-      <c r="I9" s="6" t="n"/>
-      <c r="J9" s="6" t="inlineStr">
-        <is>
-          <t>Sustentado</t>
-        </is>
-      </c>
-      <c r="K9" s="6" t="n"/>
-      <c r="L9" s="6" t="inlineStr"/>
-      <c r="M9" s="6" t="inlineStr"/>
-    </row>
-    <row r="10">
-      <c r="A10" s="12" t="n">
-        <v>24</v>
-      </c>
-      <c r="B10" s="12" t="inlineStr">
-        <is>
-          <t>NIDE</t>
-        </is>
-      </c>
-      <c r="C10" s="12" t="inlineStr">
-        <is>
-          <t>Construcción del modelo de calidad para la clasificación del uso del suelo en el ordenamiento territorial enmarcado en la infraestructura de datos espaciales para la administración de tierras</t>
-        </is>
-      </c>
-      <c r="D10" s="12" t="n">
-        <v>2022</v>
-      </c>
-      <c r="E10" s="12" t="n"/>
-      <c r="F10" s="12" t="inlineStr">
-        <is>
-          <t>Luz Angela Rocha Salamanca, Moises German Poyatos Benadero</t>
-        </is>
-      </c>
-      <c r="G10" s="12" t="inlineStr">
-        <is>
-          <t>Laura Melissa Manrique Chacon</t>
-        </is>
-      </c>
-      <c r="H10" s="12" t="n"/>
-      <c r="I10" s="12" t="n"/>
-      <c r="J10" s="12" t="inlineStr">
-        <is>
-          <t>Sustentado</t>
-        </is>
-      </c>
-      <c r="K10" s="12" t="n"/>
-      <c r="L10" s="12" t="inlineStr"/>
-      <c r="M10" s="12" t="inlineStr"/>
-    </row>
-    <row r="11">
-      <c r="A11" s="6" t="n">
-        <v>25</v>
-      </c>
-      <c r="B11" s="6" t="inlineStr">
-        <is>
-          <t>NIDE</t>
-        </is>
-      </c>
-      <c r="C11" s="6" t="inlineStr">
-        <is>
-          <t>Modelo de una infraestructura de posicionamiento como soporte a la construcción de una Sociedad Espacialmente Habilitada en Bogotá.</t>
-        </is>
-      </c>
-      <c r="D11" s="6" t="n">
-        <v>2024</v>
-      </c>
-      <c r="E11" s="6" t="n"/>
-      <c r="F11" s="6" t="inlineStr">
-        <is>
-          <t>Luz Angela Rocha Salamanca</t>
-        </is>
-      </c>
-      <c r="G11" s="6" t="inlineStr">
-        <is>
-          <t>Robert Andres Pulido Arias</t>
-        </is>
-      </c>
-      <c r="H11" s="6" t="n"/>
-      <c r="I11" s="6" t="n"/>
-      <c r="J11" s="6" t="inlineStr">
-        <is>
-          <t>Sustentado</t>
-        </is>
-      </c>
-      <c r="K11" s="6" t="n"/>
-      <c r="L11" s="6" t="inlineStr"/>
-      <c r="M11" s="6" t="inlineStr"/>
-    </row>
-    <row r="12">
-      <c r="A12" s="12" t="n">
-        <v>26</v>
-      </c>
-      <c r="B12" s="12" t="inlineStr">
-        <is>
-          <t>NIDE</t>
-        </is>
-      </c>
-      <c r="C12" s="12" t="inlineStr">
-        <is>
-          <t>Modelo para la evaluación de la calidad de agua utilizando imágenes de satélite, a partir de las concentraciones fisicoquímicas</t>
-        </is>
-      </c>
-      <c r="D12" s="12" t="n">
-        <v>2022</v>
-      </c>
-      <c r="E12" s="12" t="n"/>
-      <c r="F12" s="12" t="inlineStr">
-        <is>
-          <t>Luz Angela Rocha Salamanca</t>
-        </is>
-      </c>
-      <c r="G12" s="12" t="inlineStr">
-        <is>
-          <t>Luis Manuel Guerrero Buelvas</t>
-        </is>
-      </c>
-      <c r="H12" s="12" t="n"/>
-      <c r="I12" s="12" t="n"/>
-      <c r="J12" s="12" t="inlineStr">
-        <is>
-          <t>Sustentado</t>
-        </is>
-      </c>
-      <c r="K12" s="12" t="n"/>
-      <c r="L12" s="12" t="inlineStr"/>
-      <c r="M12" s="12" t="inlineStr"/>
-    </row>
-    <row r="13">
-      <c r="A13" s="6" t="n">
-        <v>30</v>
-      </c>
-      <c r="B13" s="6" t="inlineStr">
-        <is>
-          <t>NIDE</t>
-        </is>
-      </c>
-      <c r="C13" s="6" t="inlineStr">
-        <is>
-          <t>Modelo semántico para trayectorias de puntos en movimiento</t>
-        </is>
-      </c>
-      <c r="D13" s="6" t="n">
-        <v>2022</v>
-      </c>
-      <c r="E13" s="6" t="n"/>
-      <c r="F13" s="6" t="inlineStr">
-        <is>
-          <t>Alvaro Enrique Ortiz Davila</t>
-        </is>
-      </c>
-      <c r="G13" s="6" t="inlineStr">
-        <is>
-          <t>Nelson David Martinez Aguirre</t>
-        </is>
-      </c>
-      <c r="H13" s="6" t="n"/>
-      <c r="I13" s="6" t="n"/>
-      <c r="J13" s="6" t="inlineStr">
-        <is>
-          <t>Sustentado</t>
-        </is>
-      </c>
-      <c r="K13" s="6" t="n"/>
-      <c r="L13" s="6" t="inlineStr"/>
-      <c r="M13" s="6" t="inlineStr"/>
-    </row>
-    <row r="14">
-      <c r="A14" s="12" t="n">
-        <v>32</v>
-      </c>
-      <c r="B14" s="12" t="inlineStr">
-        <is>
-          <t>GEFEM</t>
-        </is>
-      </c>
-      <c r="C14" s="12" t="inlineStr">
-        <is>
-          <t>Modelo predictivo de erupciones volcánicas a partir de MODVOLC e interferometría de radar. Caso de estudio : Volcán Galeras</t>
-        </is>
-      </c>
-      <c r="D14" s="12" t="n">
-        <v>2022</v>
-      </c>
-      <c r="E14" s="12" t="n"/>
-      <c r="F14" s="12" t="inlineStr">
-        <is>
-          <t>Rubén Javier Medina Daza</t>
-        </is>
-      </c>
-      <c r="G14" s="12" t="inlineStr">
-        <is>
-          <t>Fabio Nicolás Luna Arevalo</t>
-        </is>
-      </c>
-      <c r="H14" s="12" t="n"/>
-      <c r="I14" s="12" t="inlineStr">
-        <is>
-          <t>https://repository.udistrital.edu.co/items/52a53df9-4179-4d61-bc66-eb06706c4662</t>
-        </is>
-      </c>
-      <c r="J14" s="12" t="inlineStr">
-        <is>
-          <t>Sustentado</t>
-        </is>
-      </c>
-      <c r="K14" s="12" t="n"/>
-      <c r="L14" s="12" t="inlineStr"/>
-      <c r="M14" s="12" t="inlineStr">
-        <is>
-          <t>Grupo GEFEM confirmado mediante la base de trabajos avalados del grupo.</t>
-        </is>
-      </c>
-    </row>
-    <row r="15">
-      <c r="A15" s="6" t="n">
-        <v>35</v>
-      </c>
-      <c r="B15" s="6" t="inlineStr">
-        <is>
-          <t>GEFEM</t>
-        </is>
-      </c>
-      <c r="C15" s="6" t="inlineStr">
-        <is>
-          <t>Metodología para identificar frailejón mediante el uso de imágenes de radar: una herramienta para la conservación ambiental</t>
-        </is>
-      </c>
-      <c r="D15" s="6" t="n">
-        <v>2022</v>
-      </c>
-      <c r="E15" s="6" t="n"/>
-      <c r="F15" s="6" t="inlineStr">
-        <is>
-          <t>Luis Eduardo Castillo Mendez</t>
-        </is>
-      </c>
-      <c r="G15" s="6" t="inlineStr">
-        <is>
-          <t>Jonathan Said Sandoval Lagos</t>
-        </is>
-      </c>
-      <c r="H15" s="6" t="n"/>
-      <c r="I15" s="6" t="inlineStr">
-        <is>
-          <t>https://repository.udistrital.edu.co/items/b0f71ac7-9180-4518-b082-892ad4a54ab7</t>
-        </is>
-      </c>
-      <c r="J15" s="6" t="inlineStr">
-        <is>
-          <t>Sustentado</t>
-        </is>
-      </c>
-      <c r="K15" s="6" t="n"/>
-      <c r="L15" s="6" t="inlineStr"/>
-      <c r="M15" s="6" t="inlineStr">
-        <is>
-          <t>Grupo GEFEM confirmado mediante la base de trabajos avalados del grupo.</t>
-        </is>
-      </c>
-    </row>
-    <row r="16">
-      <c r="A16" s="12" t="n">
-        <v>36</v>
-      </c>
-      <c r="B16" s="12" t="inlineStr">
-        <is>
-          <t>GEFEM</t>
-        </is>
-      </c>
-      <c r="C16" s="12" t="inlineStr">
-        <is>
-          <t>Análisis exploratorio espacio-temporal de la delincuencia en Colombia asociada al hurto de vehículos entre los años 2010-2019 mediante la integración de técnicas de minería de datos, Geoestadística y SIG</t>
-        </is>
-      </c>
-      <c r="D16" s="12" t="n">
-        <v>2022</v>
-      </c>
-      <c r="E16" s="12" t="n"/>
-      <c r="F16" s="12" t="inlineStr">
-        <is>
-          <t>Luis Eduardo Castillo Mendez</t>
-        </is>
-      </c>
-      <c r="G16" s="12" t="inlineStr">
-        <is>
-          <t>Gabriel Hernán González Buitrago</t>
-        </is>
-      </c>
-      <c r="H16" s="12" t="n"/>
-      <c r="I16" s="12" t="inlineStr">
-        <is>
-          <t>https://repository.udistrital.edu.co/items/12dcf76f-fbc0-4501-9dd0-b7a9071a14ef</t>
-        </is>
-      </c>
-      <c r="J16" s="12" t="inlineStr">
-        <is>
-          <t>Sustentado</t>
-        </is>
-      </c>
-      <c r="K16" s="12" t="n"/>
-      <c r="L16" s="12" t="inlineStr"/>
-      <c r="M16" s="12" t="inlineStr">
-        <is>
-          <t>Grupo GEFEM confirmado mediante la base de trabajos avalados del grupo.</t>
-        </is>
-      </c>
-    </row>
-    <row r="17">
-      <c r="A17" s="6" t="n">
-        <v>48</v>
-      </c>
-      <c r="B17" s="6" t="inlineStr">
-        <is>
-          <t>GRECO</t>
-        </is>
-      </c>
-      <c r="C17" s="6" t="inlineStr">
-        <is>
-          <t>Generación de señales WDM utilizado fuentes anchas y multiplexación por división de polarización para sistemas de radio sobre fibra</t>
-        </is>
-      </c>
-      <c r="D17" s="6" t="n">
-        <v>2022</v>
-      </c>
-      <c r="E17" s="6" t="n"/>
-      <c r="F17" s="6" t="inlineStr">
-        <is>
-          <t>Gustavo Adolfo Puerto Leguizamón</t>
-        </is>
-      </c>
-      <c r="G17" s="6" t="inlineStr">
-        <is>
-          <t>Manuel Cely Mancipe</t>
-        </is>
-      </c>
-      <c r="H17" s="6" t="n"/>
-      <c r="I17" s="6" t="n"/>
-      <c r="J17" s="6" t="inlineStr">
-        <is>
-          <t>Sustentado</t>
-        </is>
-      </c>
-      <c r="K17" s="6" t="n"/>
-      <c r="L17" s="6" t="inlineStr"/>
-      <c r="M17" s="6" t="inlineStr"/>
-    </row>
-    <row r="18">
-      <c r="A18" s="12" t="n">
-        <v>49</v>
-      </c>
-      <c r="B18" s="12" t="inlineStr">
-        <is>
-          <t>GRECO</t>
-        </is>
-      </c>
-      <c r="C18" s="12" t="inlineStr">
-        <is>
-          <t>Diseño de un sistema centralizado de transmisión de portadoras de radiofrecuencia basado en radio sobre fibra futuras redes 5G</t>
-        </is>
-      </c>
-      <c r="D18" s="12" t="n">
-        <v>2023</v>
-      </c>
-      <c r="E18" s="12" t="n"/>
-      <c r="F18" s="12" t="inlineStr">
-        <is>
-          <t>Gustavo Adolfo Puerto Leguizamón</t>
-        </is>
-      </c>
-      <c r="G18" s="12" t="inlineStr">
-        <is>
-          <t>Luis Miguel Ibarra Paez</t>
-        </is>
-      </c>
-      <c r="H18" s="12" t="n"/>
-      <c r="I18" s="12" t="n"/>
-      <c r="J18" s="12" t="inlineStr">
-        <is>
-          <t>Sustentado</t>
-        </is>
-      </c>
-      <c r="K18" s="12" t="n"/>
-      <c r="L18" s="12" t="inlineStr"/>
-      <c r="M18" s="12" t="inlineStr"/>
-    </row>
-    <row r="19">
-      <c r="A19" s="6" t="n">
-        <v>50</v>
-      </c>
-      <c r="B19" s="6" t="inlineStr">
-        <is>
-          <t>GRECO</t>
-        </is>
-      </c>
-      <c r="C19" s="6" t="inlineStr">
-        <is>
-          <t>Análisis de un modelo de volcado de tráfico de redes móviles convencionales hacia un sistema de Voz sobre WiFi-VoWiFi</t>
-        </is>
-      </c>
-      <c r="D19" s="6" t="n">
-        <v>2023</v>
-      </c>
-      <c r="E19" s="6" t="n"/>
-      <c r="F19" s="6" t="inlineStr">
-        <is>
-          <t>Gustavo Adolfo Puerto Leguizamón</t>
-        </is>
-      </c>
-      <c r="G19" s="6" t="inlineStr">
-        <is>
-          <t>Rafael Oswaldo Muñoz Ortiz</t>
-        </is>
-      </c>
-      <c r="H19" s="6" t="n"/>
-      <c r="I19" s="6" t="n"/>
-      <c r="J19" s="6" t="inlineStr">
-        <is>
-          <t>Sustentado</t>
-        </is>
-      </c>
-      <c r="K19" s="6" t="n"/>
-      <c r="L19" s="6" t="inlineStr"/>
-      <c r="M19" s="6" t="inlineStr"/>
-    </row>
-    <row r="20">
-      <c r="A20" s="12" t="n">
-        <v>54</v>
-      </c>
-      <c r="B20" s="12" t="inlineStr">
-        <is>
-          <t>GRECO</t>
-        </is>
-      </c>
-      <c r="C20" s="12" t="inlineStr">
-        <is>
-          <t>Diseño de una red de acceso basada en GPON/SCM para el transporte de datos móviles en tecnología 5G</t>
-        </is>
-      </c>
-      <c r="D20" s="12" t="n">
-        <v>2022</v>
-      </c>
-      <c r="E20" s="12" t="n"/>
-      <c r="F20" s="12" t="inlineStr">
-        <is>
-          <t>Gustavo Adolfo Puerto Leguizamón</t>
-        </is>
-      </c>
-      <c r="G20" s="12" t="inlineStr">
-        <is>
-          <t>Daniel Eduardo Romero Melo</t>
-        </is>
-      </c>
-      <c r="H20" s="12" t="n"/>
-      <c r="I20" s="12" t="n"/>
-      <c r="J20" s="12" t="inlineStr">
-        <is>
-          <t>Sustentado</t>
-        </is>
-      </c>
-      <c r="K20" s="12" t="n"/>
-      <c r="L20" s="12" t="inlineStr"/>
-      <c r="M20" s="12" t="inlineStr"/>
-    </row>
-    <row r="21">
-      <c r="A21" s="6" t="n">
-        <v>55</v>
-      </c>
-      <c r="B21" s="6" t="inlineStr">
-        <is>
-          <t>GRECO</t>
-        </is>
-      </c>
-      <c r="C21" s="6" t="inlineStr">
-        <is>
-          <t>Diseño de red SCM/DWDM con detección coherente para aplicaciones 5G en banda milimétrica</t>
-        </is>
-      </c>
-      <c r="D21" s="6" t="n">
-        <v>2022</v>
-      </c>
-      <c r="E21" s="6" t="n"/>
-      <c r="F21" s="6" t="inlineStr">
-        <is>
-          <t>Gustavo Adolfo Puerto Leguizamón</t>
-        </is>
-      </c>
-      <c r="G21" s="6" t="inlineStr">
-        <is>
-          <t>Jeisson Farid Rodríguez</t>
-        </is>
-      </c>
-      <c r="H21" s="6" t="n"/>
-      <c r="I21" s="6" t="n"/>
-      <c r="J21" s="6" t="inlineStr">
-        <is>
-          <t>Sustentado</t>
-        </is>
-      </c>
-      <c r="K21" s="6" t="n"/>
-      <c r="L21" s="6" t="inlineStr"/>
-      <c r="M21" s="6" t="inlineStr"/>
-    </row>
-    <row r="22">
-      <c r="A22" s="12" t="n">
-        <v>62</v>
-      </c>
-      <c r="B22" s="12" t="inlineStr">
-        <is>
-          <t>GITEM</t>
-        </is>
-      </c>
-      <c r="C22" s="12" t="inlineStr">
-        <is>
-          <t>Un concepto de desarrollo económico</t>
-        </is>
-      </c>
-      <c r="D22" s="12" t="n">
-        <v>2024</v>
-      </c>
-      <c r="E22" s="12" t="n"/>
-      <c r="F22" s="12" t="inlineStr">
-        <is>
-          <t>JAIME HERNANDO PENA RODRIGUEZ</t>
-        </is>
-      </c>
-      <c r="G22" s="12" t="inlineStr">
-        <is>
-          <t>EDISON RAMIREZ TOVAR</t>
-        </is>
-      </c>
-      <c r="H22" s="12" t="n"/>
-      <c r="I22" s="12" t="n"/>
-      <c r="J22" s="12" t="inlineStr">
-        <is>
-          <t>Sustentado</t>
-        </is>
-      </c>
-      <c r="K22" s="12" t="n"/>
-      <c r="L22" s="12" t="inlineStr"/>
-      <c r="M22" s="12" t="inlineStr"/>
-    </row>
-    <row r="23">
-      <c r="A23" s="6" t="n">
-        <v>150</v>
-      </c>
-      <c r="B23" s="6" t="inlineStr">
-        <is>
-          <t>LIDER</t>
-        </is>
-      </c>
-      <c r="C23" s="6" t="inlineStr">
-        <is>
-          <t>DISEÑO DE UN SISTEMA DE MONITOREO DE TEMPERATURA DE LACTANTES, UTILIZANDO METODOLOGÍA SCRUM Y TECNOLOGÍAS DEL INTERNET DE LAS COSAS (IOT)</t>
-        </is>
-      </c>
-      <c r="D23" s="6" t="n">
-        <v>2024</v>
-      </c>
-      <c r="E23" s="6" t="n"/>
-      <c r="F23" s="6" t="inlineStr">
-        <is>
-          <t>Roberto Ferro Escobar</t>
-        </is>
-      </c>
-      <c r="G23" s="6" t="inlineStr">
-        <is>
-          <t>María Alejandra Quevedo Vera</t>
-        </is>
-      </c>
-      <c r="H23" s="6" t="inlineStr">
-        <is>
-          <t>Acta 011-2024 (Nota: 5.0)</t>
-        </is>
-      </c>
-      <c r="I23" s="6" t="n"/>
-      <c r="J23" s="6" t="inlineStr">
-        <is>
-          <t>Sustentado</t>
-        </is>
-      </c>
-      <c r="K23" s="6" t="n"/>
-      <c r="L23" s="6" t="inlineStr"/>
-      <c r="M23" s="6" t="inlineStr">
-        <is>
-          <t>Sustentación aprobada con calificación 5.0 verificada en Acta de Sustentación No. 011-2024.</t>
-        </is>
-      </c>
-    </row>
-  </sheetData>
-  <autoFilter ref="A4:M23"/>
-  <mergeCells count="2">
-    <mergeCell ref="A2:M2"/>
-    <mergeCell ref="A1:M1"/>
-  </mergeCells>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -6129,22 +5115,22 @@
       </c>
     </row>
     <row r="3" ht="30" customHeight="1">
-      <c r="A3" s="11" t="inlineStr">
+      <c r="A3" s="10" t="inlineStr">
         <is>
           <t>Fuente</t>
         </is>
       </c>
-      <c r="B3" s="11" t="inlineStr">
+      <c r="B3" s="10" t="inlineStr">
         <is>
           <t>Registros incorporados</t>
         </is>
       </c>
-      <c r="C3" s="11" t="inlineStr">
+      <c r="C3" s="10" t="inlineStr">
         <is>
           <t>Uso en el consolidado</t>
         </is>
       </c>
-      <c r="D3" s="11" t="inlineStr">
+      <c r="D3" s="10" t="inlineStr">
         <is>
           <t>Observación</t>
         </is>
@@ -6171,20 +5157,20 @@
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="12" t="inlineStr">
+      <c r="A5" s="11" t="inlineStr">
         <is>
           <t>MCIC - Base de datos V2.xlsx</t>
         </is>
       </c>
-      <c r="B5" s="12" t="n">
+      <c r="B5" s="11" t="n">
         <v>49</v>
       </c>
-      <c r="C5" s="12" t="inlineStr">
+      <c r="C5" s="11" t="inlineStr">
         <is>
           <t>Registros nuevos</t>
         </is>
       </c>
-      <c r="D5" s="12" t="inlineStr">
+      <c r="D5" s="11" t="inlineStr">
         <is>
           <t>Se filtraron sustentaciones, grados y actas de pasantía de 2022 a 2026.</t>
         </is>
@@ -6211,20 +5197,20 @@
       </c>
     </row>
     <row r="7">
-      <c r="A7" s="12" t="inlineStr">
+      <c r="A7" s="11" t="inlineStr">
         <is>
           <t>MCIC - Base de datos V2.xlsx</t>
         </is>
       </c>
-      <c r="B7" s="12" t="n">
+      <c r="B7" s="11" t="n">
         <v>8</v>
       </c>
-      <c r="C7" s="12" t="inlineStr">
+      <c r="C7" s="11" t="inlineStr">
         <is>
           <t>Actualización de grupo</t>
         </is>
       </c>
-      <c r="D7" s="12" t="inlineStr">
+      <c r="D7" s="11" t="inlineStr">
         <is>
           <t>Permitió identificar el grupo de ocho registros previamente no especificados.</t>
         </is>
@@ -6251,20 +5237,20 @@
       </c>
     </row>
     <row r="9">
-      <c r="A9" s="12" t="inlineStr">
+      <c r="A9" s="11" t="inlineStr">
         <is>
           <t>MCIC - Base de datos INVESTIGACION.xlsx</t>
         </is>
       </c>
-      <c r="B9" s="12" t="n">
+      <c r="B9" s="11" t="n">
         <v>2</v>
       </c>
-      <c r="C9" s="12" t="inlineStr">
+      <c r="C9" s="11" t="inlineStr">
         <is>
           <t>Registros cruzados</t>
         </is>
       </c>
-      <c r="D9" s="12" t="inlineStr">
+      <c r="D9" s="11" t="inlineStr">
         <is>
           <t>Dos coincidencias integradas sin duplicación.</t>
         </is>
@@ -6291,20 +5277,20 @@
       </c>
     </row>
     <row r="11">
-      <c r="A11" s="12" t="inlineStr">
+      <c r="A11" s="11" t="inlineStr">
         <is>
           <t>MCIC - Base de datos INVESTIGACION.xlsx</t>
         </is>
       </c>
-      <c r="B11" s="12" t="n">
+      <c r="B11" s="11" t="n">
         <v>1</v>
       </c>
-      <c r="C11" s="12" t="inlineStr">
+      <c r="C11" s="11" t="inlineStr">
         <is>
           <t>Diferencia por validar</t>
         </is>
       </c>
-      <c r="D11" s="12" t="inlineStr">
+      <c r="D11" s="11" t="inlineStr">
         <is>
           <t>Un registro presenta grupos distintos en las fuentes: GITUD y GIIRA.</t>
         </is>
@@ -6331,20 +5317,20 @@
       </c>
     </row>
     <row r="13">
-      <c r="A13" s="12" t="inlineStr">
+      <c r="A13" s="11" t="inlineStr">
         <is>
           <t>Programación sustentaciones.xlsx</t>
         </is>
       </c>
-      <c r="B13" s="12" t="n">
+      <c r="B13" s="11" t="n">
         <v>15</v>
       </c>
-      <c r="C13" s="12" t="inlineStr">
+      <c r="C13" s="11" t="inlineStr">
         <is>
           <t>Registros nuevos</t>
         </is>
       </c>
-      <c r="D13" s="12" t="inlineStr">
+      <c r="D13" s="11" t="inlineStr">
         <is>
           <t>Sustentaciones efectivamente realizadas y registradas en 2026.</t>
         </is>
@@ -6371,20 +5357,20 @@
       </c>
     </row>
     <row r="15">
-      <c r="A15" s="12" t="inlineStr">
+      <c r="A15" s="11" t="inlineStr">
         <is>
           <t>Programación sustentaciones.xlsx</t>
         </is>
       </c>
-      <c r="B15" s="12" t="n">
+      <c r="B15" s="11" t="n">
         <v>11</v>
       </c>
-      <c r="C15" s="12" t="inlineStr">
+      <c r="C15" s="11" t="inlineStr">
         <is>
           <t>Casos pendientes</t>
         </is>
       </c>
-      <c r="D15" s="12" t="inlineStr">
+      <c r="D15" s="11" t="inlineStr">
         <is>
           <t>Casos programados o radicados sin sustentación efectiva: diez registros nuevos y uno reclasificado.</t>
         </is>
@@ -6411,20 +5397,20 @@
       </c>
     </row>
     <row r="17">
-      <c r="A17" s="12" t="inlineStr">
+      <c r="A17" s="11" t="inlineStr">
         <is>
           <t>Trabajos de Grado Avalados – Maestría en Ciencias de la Información y las Comunicaciones (2022–2026) (1).xlsx</t>
         </is>
       </c>
-      <c r="B17" s="12" t="n">
+      <c r="B17" s="11" t="n">
         <v>17</v>
       </c>
-      <c r="C17" s="12" t="inlineStr">
+      <c r="C17" s="11" t="inlineStr">
         <is>
           <t>Registros cruzados GEFEM</t>
         </is>
       </c>
-      <c r="D17" s="12" t="inlineStr">
+      <c r="D17" s="11" t="inlineStr">
         <is>
           <t>Los 17 registros ya existían y contaban con enlace RIUD: ocho conservaron GEFEM, ocho se actualizaron desde grupo no especificado y uno presentó diferencia con INTERNET INTELIGENTE.</t>
         </is>
@@ -6451,18 +5437,18 @@
       </c>
     </row>
     <row r="19">
-      <c r="A19" s="12" t="inlineStr">
+      <c r="A19" s="11" t="inlineStr">
         <is>
           <t>Control</t>
         </is>
       </c>
-      <c r="B19" s="12" t="inlineStr">
+      <c r="B19" s="11" t="inlineStr">
         <is>
           <t>Resultado</t>
         </is>
       </c>
-      <c r="C19" s="12" t="n"/>
-      <c r="D19" s="12" t="n"/>
+      <c r="C19" s="11" t="n"/>
+      <c r="D19" s="11" t="n"/>
     </row>
     <row r="20">
       <c r="A20" s="6" t="inlineStr">
@@ -6479,18 +5465,18 @@
       <c r="D20" s="6" t="n"/>
     </row>
     <row r="21">
-      <c r="A21" s="12" t="inlineStr">
+      <c r="A21" s="11" t="inlineStr">
         <is>
           <t>Trabajos sustentados</t>
         </is>
       </c>
-      <c r="B21" s="12" t="inlineStr">
+      <c r="B21" s="11" t="inlineStr">
         <is>
           <t>133 registros</t>
         </is>
       </c>
-      <c r="C21" s="12" t="n"/>
-      <c r="D21" s="12" t="n"/>
+      <c r="C21" s="11" t="n"/>
+      <c r="D21" s="11" t="n"/>
     </row>
     <row r="22">
       <c r="A22" s="6" t="inlineStr">
@@ -6507,18 +5493,18 @@
       <c r="D22" s="6" t="n"/>
     </row>
     <row r="23">
-      <c r="A23" s="12" t="inlineStr">
+      <c r="A23" s="11" t="inlineStr">
         <is>
           <t>Registros adicionales</t>
         </is>
       </c>
-      <c r="B23" s="12" t="inlineStr">
+      <c r="B23" s="11" t="inlineStr">
         <is>
           <t>88</t>
         </is>
       </c>
-      <c r="C23" s="12" t="n"/>
-      <c r="D23" s="12" t="n"/>
+      <c r="C23" s="11" t="n"/>
+      <c r="D23" s="11" t="n"/>
     </row>
     <row r="24">
       <c r="A24" s="6" t="inlineStr">
@@ -6535,18 +5521,18 @@
       <c r="D24" s="6" t="n"/>
     </row>
     <row r="25">
-      <c r="A25" s="12" t="inlineStr">
+      <c r="A25" s="11" t="inlineStr">
         <is>
           <t>Grupos identificados</t>
         </is>
       </c>
-      <c r="B25" s="12" t="inlineStr">
+      <c r="B25" s="11" t="inlineStr">
         <is>
           <t>25</t>
         </is>
       </c>
-      <c r="C25" s="12" t="n"/>
-      <c r="D25" s="12" t="n"/>
+      <c r="C25" s="11" t="n"/>
+      <c r="D25" s="11" t="n"/>
     </row>
     <row r="26">
       <c r="A26" s="6" t="inlineStr">
@@ -6563,18 +5549,18 @@
       <c r="D26" s="6" t="n"/>
     </row>
     <row r="27">
-      <c r="A27" s="12" t="inlineStr">
+      <c r="A27" s="11" t="inlineStr">
         <is>
           <t>Enlaces RIUD disponibles</t>
         </is>
       </c>
-      <c r="B27" s="12" t="inlineStr">
+      <c r="B27" s="11" t="inlineStr">
         <is>
           <t>17 registros</t>
         </is>
       </c>
-      <c r="C27" s="12" t="n"/>
-      <c r="D27" s="12" t="n"/>
+      <c r="C27" s="11" t="n"/>
+      <c r="D27" s="11" t="n"/>
     </row>
     <row r="28">
       <c r="A28" s="6" t="inlineStr">
@@ -6591,14 +5577,14 @@
       <c r="D28" s="6" t="n"/>
     </row>
     <row r="29">
-      <c r="A29" s="12" t="inlineStr">
+      <c r="A29" s="11" t="inlineStr">
         <is>
           <t>Método: se incluyeron todos los casos localizados para la ventana 2022–2026 vinculados con grupos de investigación. Los registros con fecha efectiva de sustentación, año de grado, acta de pasantía o enlace RIUD se clasificaron como sustentados. Los casos únicamente programados, radicados o avalados por un grupo se conservaron como no sustentados o sin sustentación verificada y sí se contabilizan en los gráficos y en la matriz, diferenciados por estado. Los años de la base LIDER corresponden a la emisión del aval y no sustituyen el año efectivo de sustentación. La base GEFEM se cruzó completamente con registros existentes que ya contaban con enlace RIUD. Para los grupos de investigación se contrastaron las cartas de aval, radicaciones y expedientes documentales en Bronze. Las diferencias entre fuentes se conservaron en la columna Observación de cruce.</t>
         </is>
       </c>
-      <c r="B29" s="12" t="n"/>
-      <c r="C29" s="12" t="n"/>
-      <c r="D29" s="12" t="n"/>
+      <c r="B29" s="11" t="n"/>
+      <c r="C29" s="11" t="n"/>
+      <c r="D29" s="11" t="n"/>
     </row>
   </sheetData>
   <mergeCells count="1">

--- a/Data/Bronze/MCIC-PROFUNDIZACION/Procesos de Renocavion y acreditación/Plan de Mejoramiento/FACTOR 8. APORTES DE LA INVESTIGACIÓN, LA INNOVACIÓN, EL DESARROLLO TECNOLÓGICO Y LA CREACIÓN ASOCIADOS AL PROGRAMA ACADÉMICO/b. Socialización y vinculación de actividades de investigación/F8_Trabajos_de_grado_por_grupo_Profundizacion.xlsx
+++ b/Data/Bronze/MCIC-PROFUNDIZACION/Procesos de Renocavion y acreditación/Plan de Mejoramiento/FACTOR 8. APORTES DE LA INVESTIGACIÓN, LA INNOVACIÓN, EL DESARROLLO TECNOLÓGICO Y LA CREACIÓN ASOCIADOS AL PROGRAMA ACADÉMICO/b. Socialización y vinculación de actividades de investigación/F8_Trabajos_de_grado_por_grupo_Profundizacion.xlsx
@@ -10,12 +10,13 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Resumen" sheetId="1" state="visible" r:id="rId1"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Comparativo por grupo" sheetId="2" state="visible" r:id="rId2"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Consolidado" sheetId="3" state="visible" r:id="rId3"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Pendientes sustentación" sheetId="4" state="visible" r:id="rId4"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Fuentes y calidad" sheetId="5" state="visible" r:id="rId5"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Pendientes por sustentar" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Tesis con documento" sheetId="5" state="visible" r:id="rId5"/>
   </sheets>
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'Consolidado'!$A$3:$M$58</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'Pendientes sustentación'!$A$3:$M$11</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'Pendientes por sustentar'!$A$3:$M$11</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="4" hidden="1">'Tesis con documento'!$A$4:$G$8</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -659,7 +660,7 @@
       </c>
       <c r="E9" s="8" t="inlineStr">
         <is>
-          <t>Pendientes / sin verificación</t>
+          <t>Pendientes por sustentar</t>
         </is>
       </c>
       <c r="G9" s="8" t="inlineStr">
@@ -707,7 +708,7 @@
       </c>
       <c r="D16" s="10" t="inlineStr">
         <is>
-          <t>No sustentados</t>
+          <t>Pendientes por sustentar</t>
         </is>
       </c>
       <c r="E16" s="10" t="inlineStr">
@@ -737,7 +738,7 @@
         <v>7</v>
       </c>
       <c r="E17" s="6" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="F17" s="6" t="n">
         <v>0</v>
@@ -781,7 +782,7 @@
         <v>15</v>
       </c>
       <c r="E19" s="6" t="n">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="F19" s="6" t="n">
         <v>3</v>
@@ -807,7 +808,7 @@
       </c>
       <c r="C22" s="10" t="inlineStr">
         <is>
-          <t>No sustentados</t>
+          <t>Pendientes por sustentar</t>
         </is>
       </c>
       <c r="D22" s="10" t="inlineStr">
@@ -1108,7 +1109,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D30"/>
+  <dimension ref="A1:D29"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="50" customWidth="1" min="1" max="1"/>
@@ -1176,27 +1177,27 @@
     <row r="7">
       <c r="A7" s="6" t="inlineStr">
         <is>
-          <t>LIDER</t>
+          <t>INTERNET INTELIGENTE</t>
         </is>
       </c>
       <c r="B7" s="6" t="n">
-        <v>7</v>
+        <v>2</v>
       </c>
       <c r="C7" s="6" t="n">
-        <v>3</v>
+        <v>8</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="11" t="inlineStr">
         <is>
-          <t>INTERNET INTELIGENTE</t>
+          <t>LIDER</t>
         </is>
       </c>
       <c r="B8" s="11" t="n">
-        <v>2</v>
+        <v>7</v>
       </c>
       <c r="C8" s="11" t="n">
-        <v>8</v>
+        <v>3</v>
       </c>
     </row>
     <row r="9">
@@ -1228,46 +1229,46 @@
     <row r="11">
       <c r="A11" s="6" t="inlineStr">
         <is>
-          <t>GRECO</t>
+          <t>Multimedia Interactiva y Animación Digital</t>
         </is>
       </c>
       <c r="B11" s="6" t="n">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="C11" s="6" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="11" t="inlineStr">
         <is>
-          <t>GIIRA</t>
+          <t>GRECO</t>
         </is>
       </c>
       <c r="B12" s="11" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="C12" s="11" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="6" t="inlineStr">
         <is>
-          <t>Multimedia Interactiva y Animación Digital</t>
+          <t>GIIRA</t>
         </is>
       </c>
       <c r="B13" s="6" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="C13" s="6" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="11" t="inlineStr">
         <is>
-          <t>GITUD</t>
+          <t>INTECSE</t>
         </is>
       </c>
       <c r="B14" s="11" t="n">
@@ -1280,27 +1281,27 @@
     <row r="15">
       <c r="A15" s="6" t="inlineStr">
         <is>
-          <t>INTECSE</t>
+          <t>LASER</t>
         </is>
       </c>
       <c r="B15" s="6" t="n">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="C15" s="6" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="11" t="inlineStr">
         <is>
-          <t>LASER</t>
+          <t>GITUD</t>
         </is>
       </c>
       <c r="B16" s="11" t="n">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="C16" s="11" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="17">
@@ -1345,7 +1346,7 @@
     <row r="20">
       <c r="A20" s="11" t="inlineStr">
         <is>
-          <t>GICOECOL</t>
+          <t>ARMOS</t>
         </is>
       </c>
       <c r="B20" s="11" t="n">
@@ -1358,7 +1359,7 @@
     <row r="21">
       <c r="A21" s="6" t="inlineStr">
         <is>
-          <t>ARMOS</t>
+          <t>GICOECOL</t>
         </is>
       </c>
       <c r="B21" s="6" t="n">
@@ -1384,20 +1385,20 @@
     <row r="23">
       <c r="A23" s="6" t="inlineStr">
         <is>
-          <t>DIMSI</t>
+          <t>Bionanotecnología</t>
         </is>
       </c>
       <c r="B23" s="6" t="n">
+        <v>1</v>
+      </c>
+      <c r="C23" s="6" t="n">
         <v>0</v>
-      </c>
-      <c r="C23" s="6" t="n">
-        <v>1</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" s="11" t="inlineStr">
         <is>
-          <t>LASER LAMIC</t>
+          <t>COMPLEX UD</t>
         </is>
       </c>
       <c r="B24" s="11" t="n">
@@ -1410,46 +1411,46 @@
     <row r="25">
       <c r="A25" s="6" t="inlineStr">
         <is>
-          <t>PROPROBOS</t>
+          <t>DIMSI</t>
         </is>
       </c>
       <c r="B25" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="C25" s="6" t="n">
         <v>1</v>
-      </c>
-      <c r="C25" s="6" t="n">
-        <v>0</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" s="11" t="inlineStr">
         <is>
-          <t>CEPMS</t>
+          <t>XUE</t>
         </is>
       </c>
       <c r="B26" s="11" t="n">
+        <v>0</v>
+      </c>
+      <c r="C26" s="11" t="n">
         <v>1</v>
-      </c>
-      <c r="C26" s="11" t="n">
-        <v>0</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" s="6" t="inlineStr">
         <is>
-          <t>XUE</t>
+          <t>CEPMS</t>
         </is>
       </c>
       <c r="B27" s="6" t="n">
+        <v>1</v>
+      </c>
+      <c r="C27" s="6" t="n">
         <v>0</v>
-      </c>
-      <c r="C27" s="6" t="n">
-        <v>1</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" s="11" t="inlineStr">
         <is>
-          <t>COMPLEX UD</t>
+          <t>PROPROBOS</t>
         </is>
       </c>
       <c r="B28" s="11" t="n">
@@ -1469,19 +1470,6 @@
         <v>1</v>
       </c>
       <c r="C29" s="6" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="30">
-      <c r="A30" s="11" t="inlineStr">
-        <is>
-          <t>Bionanotecnología</t>
-        </is>
-      </c>
-      <c r="B30" s="11" t="n">
-        <v>1</v>
-      </c>
-      <c r="C30" s="11" t="n">
         <v>0</v>
       </c>
     </row>
@@ -5098,497 +5086,214 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D29"/>
+  <dimension ref="A1:G8"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="50" customWidth="1" min="1" max="1"/>
-    <col width="20" customWidth="1" min="2" max="2"/>
+    <col width="26" customWidth="1" min="1" max="1"/>
+    <col width="70" customWidth="1" min="2" max="2"/>
     <col width="30" customWidth="1" min="3" max="3"/>
-    <col width="80" customWidth="1" min="4" max="4"/>
+    <col width="30" customWidth="1" min="4" max="4"/>
+    <col width="7" customWidth="1" min="5" max="5"/>
+    <col width="20" customWidth="1" min="6" max="6"/>
+    <col width="60" customWidth="1" min="7" max="7"/>
   </cols>
   <sheetData>
     <row r="1" ht="24" customHeight="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Fuentes, alcance y control de calidad (tomado del consolidado original)</t>
-        </is>
-      </c>
-    </row>
-    <row r="3" ht="30" customHeight="1">
-      <c r="A3" s="10" t="inlineStr">
-        <is>
-          <t>Fuente</t>
-        </is>
-      </c>
-      <c r="B3" s="10" t="inlineStr">
-        <is>
-          <t>Registros incorporados</t>
-        </is>
-      </c>
-      <c r="C3" s="10" t="inlineStr">
-        <is>
-          <t>Uso en el consolidado</t>
-        </is>
-      </c>
-      <c r="D3" s="10" t="inlineStr">
-        <is>
-          <t>Observación</t>
-        </is>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" s="6" t="inlineStr">
-        <is>
-          <t>Siete archivos de grupos de investigación</t>
-        </is>
-      </c>
-      <c r="B4" s="6" t="n">
-        <v>62</v>
-      </c>
-      <c r="C4" s="6" t="inlineStr">
-        <is>
-          <t>Base inicial</t>
-        </is>
-      </c>
-      <c r="D4" s="6" t="inlineStr">
-        <is>
-          <t>Aportaron 62 registros; 17 contenían enlace RIUD.</t>
+          <t>Trabajos de grado con documento completo — Profundización</t>
+        </is>
+      </c>
+    </row>
+    <row r="2" ht="16" customHeight="1">
+      <c r="A2" s="2" t="inlineStr">
+        <is>
+          <t>Documentos disponibles en la carpeta «Anexos / Tesis».</t>
+        </is>
+      </c>
+    </row>
+    <row r="4" ht="30" customHeight="1">
+      <c r="A4" s="10" t="inlineStr">
+        <is>
+          <t>Grupo de investigación</t>
+        </is>
+      </c>
+      <c r="B4" s="10" t="inlineStr">
+        <is>
+          <t>Título</t>
+        </is>
+      </c>
+      <c r="C4" s="10" t="inlineStr">
+        <is>
+          <t>Estudiante(s)</t>
+        </is>
+      </c>
+      <c r="D4" s="10" t="inlineStr">
+        <is>
+          <t>Director(es)</t>
+        </is>
+      </c>
+      <c r="E4" s="10" t="inlineStr">
+        <is>
+          <t>Año</t>
+        </is>
+      </c>
+      <c r="F4" s="10" t="inlineStr">
+        <is>
+          <t>Estado de sustentación</t>
+        </is>
+      </c>
+      <c r="G4" s="10" t="inlineStr">
+        <is>
+          <t>Documento (anexo)</t>
         </is>
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="11" t="inlineStr">
-        <is>
-          <t>MCIC - Base de datos V2.xlsx</t>
-        </is>
-      </c>
-      <c r="B5" s="11" t="n">
-        <v>49</v>
-      </c>
-      <c r="C5" s="11" t="inlineStr">
-        <is>
-          <t>Registros nuevos</t>
-        </is>
-      </c>
-      <c r="D5" s="11" t="inlineStr">
-        <is>
-          <t>Se filtraron sustentaciones, grados y actas de pasantía de 2022 a 2026.</t>
+      <c r="A5" s="6" t="inlineStr">
+        <is>
+          <t>Multimedia Interactiva y Animación Digital</t>
+        </is>
+      </c>
+      <c r="B5" s="6" t="inlineStr">
+        <is>
+          <t>Diseño de una plataforma para la ejecución de modelos de predicción sobre el mercado de divisas mediante machine learning</t>
+        </is>
+      </c>
+      <c r="C5" s="6" t="inlineStr">
+        <is>
+          <t>Kevin Steven Gordillo Orjuela</t>
+        </is>
+      </c>
+      <c r="D5" s="6" t="inlineStr">
+        <is>
+          <t>Paulo Alonso Gaona García</t>
+        </is>
+      </c>
+      <c r="E5" s="6" t="n">
+        <v>2023</v>
+      </c>
+      <c r="F5" s="6" t="inlineStr">
+        <is>
+          <t>Sustentado</t>
+        </is>
+      </c>
+      <c r="G5" s="6" t="inlineStr">
+        <is>
+          <t>Tesis - Diseño de una plataforma para la ejecución de modelos de predicción sobre el mercado de di.pdf</t>
         </is>
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="6" t="inlineStr">
-        <is>
-          <t>MCIC - Base de datos V2.xlsx</t>
-        </is>
-      </c>
-      <c r="B6" s="6" t="n">
-        <v>27</v>
-      </c>
-      <c r="C6" s="6" t="inlineStr">
-        <is>
-          <t>Registros cruzados</t>
-        </is>
-      </c>
-      <c r="D6" s="6" t="inlineStr">
-        <is>
-          <t>Coincidencias por estudiante o título con la base inicial.</t>
+      <c r="A6" s="11" t="inlineStr">
+        <is>
+          <t>Multimedia Interactiva y Animación Digital</t>
+        </is>
+      </c>
+      <c r="B6" s="11" t="inlineStr">
+        <is>
+          <t>Diseño de modelo arquitectónico asíncrono para la implementación de servicios de computación sin servidor en la infraestructura de nube privada de IFX NETWORKS.</t>
+        </is>
+      </c>
+      <c r="C6" s="11" t="inlineStr">
+        <is>
+          <t>Breitner Enrique González Angarita</t>
+        </is>
+      </c>
+      <c r="D6" s="11" t="inlineStr">
+        <is>
+          <t>Paulo Alonso Gaona García</t>
+        </is>
+      </c>
+      <c r="E6" s="11" t="n">
+        <v>2025</v>
+      </c>
+      <c r="F6" s="11" t="inlineStr">
+        <is>
+          <t>Sustentado</t>
+        </is>
+      </c>
+      <c r="G6" s="11" t="inlineStr">
+        <is>
+          <t>Tesis - Diseño de modelo arquitectónico asíncrono para la implementación de servicios de computaci.pdf</t>
         </is>
       </c>
     </row>
     <row r="7">
-      <c r="A7" s="11" t="inlineStr">
-        <is>
-          <t>MCIC - Base de datos V2.xlsx</t>
-        </is>
-      </c>
-      <c r="B7" s="11" t="n">
-        <v>8</v>
-      </c>
-      <c r="C7" s="11" t="inlineStr">
-        <is>
-          <t>Actualización de grupo</t>
-        </is>
-      </c>
-      <c r="D7" s="11" t="inlineStr">
-        <is>
-          <t>Permitió identificar el grupo de ocho registros previamente no especificados.</t>
+      <c r="A7" s="6" t="inlineStr">
+        <is>
+          <t>Multimedia Interactiva y Animación Digital</t>
+        </is>
+      </c>
+      <c r="B7" s="6" t="inlineStr">
+        <is>
+          <t>Modelo para la evaluación de la calidad intrínseca y dinámica de los datos abiertos sector salud en Bogotá D.C. basado en Machine Learning</t>
+        </is>
+      </c>
+      <c r="C7" s="6" t="inlineStr">
+        <is>
+          <t>Alvaro Varon Capera</t>
+        </is>
+      </c>
+      <c r="D7" s="6" t="inlineStr">
+        <is>
+          <t>Paulo Alonso Gaona García</t>
+        </is>
+      </c>
+      <c r="E7" s="6" t="n">
+        <v>2025</v>
+      </c>
+      <c r="F7" s="6" t="inlineStr">
+        <is>
+          <t>Sustentado</t>
+        </is>
+      </c>
+      <c r="G7" s="6" t="inlineStr">
+        <is>
+          <t>Tesis - Modelo para la evaluación de la calidad intrínseca y dinámica de los datos abiertos sector.pdf</t>
         </is>
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="6" t="inlineStr">
-        <is>
-          <t>MCIC - Base de datos INVESTIGACION.xlsx</t>
-        </is>
-      </c>
-      <c r="B8" s="6" t="n">
-        <v>5</v>
-      </c>
-      <c r="C8" s="6" t="inlineStr">
-        <is>
-          <t>Registros nuevos</t>
-        </is>
-      </c>
-      <c r="D8" s="6" t="inlineStr">
-        <is>
-          <t>Trabajos con sustentación registrada en 2025 o 2026.</t>
-        </is>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" s="11" t="inlineStr">
-        <is>
-          <t>MCIC - Base de datos INVESTIGACION.xlsx</t>
-        </is>
-      </c>
-      <c r="B9" s="11" t="n">
-        <v>2</v>
-      </c>
-      <c r="C9" s="11" t="inlineStr">
-        <is>
-          <t>Registros cruzados</t>
-        </is>
-      </c>
-      <c r="D9" s="11" t="inlineStr">
-        <is>
-          <t>Dos coincidencias integradas sin duplicación.</t>
-        </is>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" s="6" t="inlineStr">
-        <is>
-          <t>MCIC - Base de datos INVESTIGACION.xlsx</t>
-        </is>
-      </c>
-      <c r="B10" s="6" t="n">
-        <v>1</v>
-      </c>
-      <c r="C10" s="6" t="inlineStr">
-        <is>
-          <t>Actualización de grupo</t>
-        </is>
-      </c>
-      <c r="D10" s="6" t="inlineStr">
-        <is>
-          <t>Se completó GEFEM para un registro previamente no especificado.</t>
-        </is>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" s="11" t="inlineStr">
-        <is>
-          <t>MCIC - Base de datos INVESTIGACION.xlsx</t>
-        </is>
-      </c>
-      <c r="B11" s="11" t="n">
-        <v>1</v>
-      </c>
-      <c r="C11" s="11" t="inlineStr">
-        <is>
-          <t>Diferencia por validar</t>
-        </is>
-      </c>
-      <c r="D11" s="11" t="inlineStr">
-        <is>
-          <t>Un registro presenta grupos distintos en las fuentes: GITUD y GIIRA.</t>
-        </is>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" s="6" t="inlineStr">
-        <is>
-          <t>MCIC - Base de datos Profundizacion.xlsx</t>
-        </is>
-      </c>
-      <c r="B12" s="6" t="n">
-        <v>4</v>
-      </c>
-      <c r="C12" s="6" t="inlineStr">
-        <is>
-          <t>Registros nuevos</t>
-        </is>
-      </c>
-      <c r="D12" s="6" t="inlineStr">
-        <is>
-          <t>Un trabajo de profundización sustentado en 2026 y tres pasantías con acta de 2025.</t>
-        </is>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" s="11" t="inlineStr">
-        <is>
-          <t>Programación sustentaciones.xlsx</t>
-        </is>
-      </c>
-      <c r="B13" s="11" t="n">
-        <v>15</v>
-      </c>
-      <c r="C13" s="11" t="inlineStr">
-        <is>
-          <t>Registros nuevos</t>
-        </is>
-      </c>
-      <c r="D13" s="11" t="inlineStr">
-        <is>
-          <t>Sustentaciones efectivamente realizadas y registradas en 2026.</t>
-        </is>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" s="6" t="inlineStr">
-        <is>
-          <t>Programación sustentaciones.xlsx</t>
-        </is>
-      </c>
-      <c r="B14" s="6" t="n">
-        <v>9</v>
-      </c>
-      <c r="C14" s="6" t="inlineStr">
-        <is>
-          <t>Registros cruzados</t>
-        </is>
-      </c>
-      <c r="D14" s="6" t="inlineStr">
-        <is>
-          <t>Se completaron fechas, actas, títulos o directores sin duplicar registros.</t>
-        </is>
-      </c>
-    </row>
-    <row r="15">
-      <c r="A15" s="11" t="inlineStr">
-        <is>
-          <t>Programación sustentaciones.xlsx</t>
-        </is>
-      </c>
-      <c r="B15" s="11" t="n">
-        <v>11</v>
-      </c>
-      <c r="C15" s="11" t="inlineStr">
-        <is>
-          <t>Casos pendientes</t>
-        </is>
-      </c>
-      <c r="D15" s="11" t="inlineStr">
-        <is>
-          <t>Casos programados o radicados sin sustentación efectiva: diez registros nuevos y uno reclasificado.</t>
-        </is>
-      </c>
-    </row>
-    <row r="16">
-      <c r="A16" s="6" t="inlineStr">
-        <is>
-          <t>Solicitud MCIC - Trabajos de grado grupop LIDER.xlsx</t>
-        </is>
-      </c>
-      <c r="B16" s="6" t="n">
-        <v>12</v>
-      </c>
-      <c r="C16" s="6" t="inlineStr">
-        <is>
-          <t>Cruce de 10 casos únicos</t>
-        </is>
-      </c>
-      <c r="D16" s="6" t="inlineStr">
-        <is>
-          <t>Cinco registros existentes fueron actualizados con el grupo LIDER y cinco casos avalados se incorporaron sin sustentación verificada; dos filas repetían trabajos con otro año de aval.</t>
-        </is>
-      </c>
-    </row>
-    <row r="17">
-      <c r="A17" s="11" t="inlineStr">
-        <is>
-          <t>Trabajos de Grado Avalados – Maestría en Ciencias de la Información y las Comunicaciones (2022–2026) (1).xlsx</t>
-        </is>
-      </c>
-      <c r="B17" s="11" t="n">
-        <v>17</v>
-      </c>
-      <c r="C17" s="11" t="inlineStr">
-        <is>
-          <t>Registros cruzados GEFEM</t>
-        </is>
-      </c>
-      <c r="D17" s="11" t="inlineStr">
-        <is>
-          <t>Los 17 registros ya existían y contaban con enlace RIUD: ocho conservaron GEFEM, ocho se actualizaron desde grupo no especificado y uno presentó diferencia con INTERNET INTELIGENTE.</t>
-        </is>
-      </c>
-    </row>
-    <row r="18">
-      <c r="A18" s="6" t="inlineStr">
-        <is>
-          <t>Directorio institucional de grupos — Unidad de Investigaciones</t>
-        </is>
-      </c>
-      <c r="B18" s="6" t="n">
-        <v>18</v>
-      </c>
-      <c r="C18" s="6" t="inlineStr">
-        <is>
-          <t>Cruce nominal de directores</t>
-        </is>
-      </c>
-      <c r="D18" s="6" t="inlineStr">
-        <is>
-          <t>Cinco asociaciones se verificaron explícitamente en el portal institucional y trece se completaron por coincidencia nominal consistente con registros ya clasificados; siete casos permanecen pendientes de validación.</t>
-        </is>
-      </c>
-    </row>
-    <row r="19">
-      <c r="A19" s="11" t="inlineStr">
-        <is>
-          <t>Control</t>
-        </is>
-      </c>
-      <c r="B19" s="11" t="inlineStr">
-        <is>
-          <t>Resultado</t>
-        </is>
-      </c>
-      <c r="C19" s="11" t="n"/>
-      <c r="D19" s="11" t="n"/>
-    </row>
-    <row r="20">
-      <c r="A20" s="6" t="inlineStr">
-        <is>
-          <t>Total de casos</t>
-        </is>
-      </c>
-      <c r="B20" s="6" t="inlineStr">
-        <is>
-          <t>148 registros</t>
-        </is>
-      </c>
-      <c r="C20" s="6" t="n"/>
-      <c r="D20" s="6" t="n"/>
-    </row>
-    <row r="21">
-      <c r="A21" s="11" t="inlineStr">
-        <is>
-          <t>Trabajos sustentados</t>
-        </is>
-      </c>
-      <c r="B21" s="11" t="inlineStr">
-        <is>
-          <t>133 registros</t>
-        </is>
-      </c>
-      <c r="C21" s="11" t="n"/>
-      <c r="D21" s="11" t="n"/>
-    </row>
-    <row r="22">
-      <c r="A22" s="6" t="inlineStr">
-        <is>
-          <t>Pendientes o sin sustentación verificada</t>
-        </is>
-      </c>
-      <c r="B22" s="6" t="inlineStr">
-        <is>
-          <t>15 registros</t>
-        </is>
-      </c>
-      <c r="C22" s="6" t="n"/>
-      <c r="D22" s="6" t="n"/>
-    </row>
-    <row r="23">
-      <c r="A23" s="11" t="inlineStr">
-        <is>
-          <t>Registros adicionales</t>
-        </is>
-      </c>
-      <c r="B23" s="11" t="inlineStr">
-        <is>
-          <t>88</t>
-        </is>
-      </c>
-      <c r="C23" s="11" t="n"/>
-      <c r="D23" s="11" t="n"/>
-    </row>
-    <row r="24">
-      <c r="A24" s="6" t="inlineStr">
-        <is>
-          <t>Coincidencias integradas sin duplicar</t>
-        </is>
-      </c>
-      <c r="B24" s="6" t="inlineStr">
-        <is>
-          <t>61</t>
-        </is>
-      </c>
-      <c r="C24" s="6" t="n"/>
-      <c r="D24" s="6" t="n"/>
-    </row>
-    <row r="25">
-      <c r="A25" s="11" t="inlineStr">
-        <is>
-          <t>Grupos identificados</t>
-        </is>
-      </c>
-      <c r="B25" s="11" t="inlineStr">
-        <is>
-          <t>25</t>
-        </is>
-      </c>
-      <c r="C25" s="11" t="n"/>
-      <c r="D25" s="11" t="n"/>
-    </row>
-    <row r="26">
-      <c r="A26" s="6" t="inlineStr">
-        <is>
-          <t>Soporte de grupo verificado</t>
-        </is>
-      </c>
-      <c r="B26" s="6" t="inlineStr">
-        <is>
-          <t>100% de casos con grupo</t>
-        </is>
-      </c>
-      <c r="C26" s="6" t="n"/>
-      <c r="D26" s="6" t="n"/>
-    </row>
-    <row r="27">
-      <c r="A27" s="11" t="inlineStr">
-        <is>
-          <t>Enlaces RIUD disponibles</t>
-        </is>
-      </c>
-      <c r="B27" s="11" t="inlineStr">
-        <is>
-          <t>17 registros</t>
-        </is>
-      </c>
-      <c r="C27" s="11" t="n"/>
-      <c r="D27" s="11" t="n"/>
-    </row>
-    <row r="28">
-      <c r="A28" s="6" t="inlineStr">
-        <is>
-          <t>Ventana temporal</t>
-        </is>
-      </c>
-      <c r="B28" s="6" t="inlineStr">
-        <is>
-          <t>2022–2026</t>
-        </is>
-      </c>
-      <c r="C28" s="6" t="n"/>
-      <c r="D28" s="6" t="n"/>
-    </row>
-    <row r="29">
-      <c r="A29" s="11" t="inlineStr">
-        <is>
-          <t>Método: se incluyeron todos los casos localizados para la ventana 2022–2026 vinculados con grupos de investigación. Los registros con fecha efectiva de sustentación, año de grado, acta de pasantía o enlace RIUD se clasificaron como sustentados. Los casos únicamente programados, radicados o avalados por un grupo se conservaron como no sustentados o sin sustentación verificada y sí se contabilizan en los gráficos y en la matriz, diferenciados por estado. Los años de la base LIDER corresponden a la emisión del aval y no sustituyen el año efectivo de sustentación. La base GEFEM se cruzó completamente con registros existentes que ya contaban con enlace RIUD. Para los grupos de investigación se contrastaron las cartas de aval, radicaciones y expedientes documentales en Bronze. Las diferencias entre fuentes se conservaron en la columna Observación de cruce.</t>
-        </is>
-      </c>
-      <c r="B29" s="11" t="n"/>
-      <c r="C29" s="11" t="n"/>
-      <c r="D29" s="11" t="n"/>
+      <c r="A8" s="11" t="inlineStr">
+        <is>
+          <t>Multimedia Interactiva y Animación Digital</t>
+        </is>
+      </c>
+      <c r="B8" s="11" t="inlineStr">
+        <is>
+          <t>Diseño de una plataforma para la ejecución de modelos de predicción sobre el mercado de divisas mediante machine learning</t>
+        </is>
+      </c>
+      <c r="C8" s="11" t="inlineStr">
+        <is>
+          <t>Kevin Steven Gordillo Orjuela</t>
+        </is>
+      </c>
+      <c r="D8" s="11" t="inlineStr">
+        <is>
+          <t>Paulo Alonso Gaona García</t>
+        </is>
+      </c>
+      <c r="E8" s="11" t="n">
+        <v>2023</v>
+      </c>
+      <c r="F8" s="11" t="inlineStr">
+        <is>
+          <t>Sustentado</t>
+        </is>
+      </c>
+      <c r="G8" s="11" t="inlineStr">
+        <is>
+          <t>Tesis - Diseño de una plataforma para la ejecución de modelos de predicción sobre el mercado de di (2).pdf</t>
+        </is>
+      </c>
     </row>
   </sheetData>
-  <mergeCells count="1">
-    <mergeCell ref="A1:D1"/>
+  <autoFilter ref="A4:G8"/>
+  <mergeCells count="2">
+    <mergeCell ref="A2:G2"/>
+    <mergeCell ref="A1:G1"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/Data/Bronze/MCIC-PROFUNDIZACION/Procesos de Renocavion y acreditación/Plan de Mejoramiento/FACTOR 8. APORTES DE LA INVESTIGACIÓN, LA INNOVACIÓN, EL DESARROLLO TECNOLÓGICO Y LA CREACIÓN ASOCIADOS AL PROGRAMA ACADÉMICO/b. Socialización y vinculación de actividades de investigación/F8_Trabajos_de_grado_por_grupo_Profundizacion.xlsx
+++ b/Data/Bronze/MCIC-PROFUNDIZACION/Procesos de Renocavion y acreditación/Plan de Mejoramiento/FACTOR 8. APORTES DE LA INVESTIGACIÓN, LA INNOVACIÓN, EL DESARROLLO TECNOLÓGICO Y LA CREACIÓN ASOCIADOS AL PROGRAMA ACADÉMICO/b. Socialización y vinculación de actividades de investigación/F8_Trabajos_de_grado_por_grupo_Profundizacion.xlsx
@@ -579,10 +579,10 @@
         </is>
       </c>
     </row>
-    <row r="2" ht="30" customHeight="1">
+    <row r="2" ht="45" customHeight="1">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Versión por modalidad del «Consolidado de trabajos de grado MCIC 2022-2026» (el libro completo del consolidado es el documento de origen). Se omiten el código estudiantil y la ruta del archivo fuente.</t>
+          <t>Versión por modalidad del «Consolidado de trabajos de grado MCIC 2022-2026» (el libro completo del consolidado es el documento de origen). Se omiten el código estudiantil y la ruta del archivo fuente. El consolidado completo está en la misma carpeta (sin el código estudiantil ni las rutas internas).</t>
         </is>
       </c>
     </row>
@@ -1203,66 +1203,66 @@
     <row r="9">
       <c r="A9" s="6" t="inlineStr">
         <is>
-          <t>GITEM</t>
+          <t>GICOGE</t>
         </is>
       </c>
       <c r="B9" s="6" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="C9" s="6" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="11" t="inlineStr">
         <is>
-          <t>GICOGE</t>
+          <t>GITEM</t>
         </is>
       </c>
       <c r="B10" s="11" t="n">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="C10" s="11" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="6" t="inlineStr">
         <is>
-          <t>Multimedia Interactiva y Animación Digital</t>
+          <t>GIIRA</t>
         </is>
       </c>
       <c r="B11" s="6" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="C11" s="6" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="11" t="inlineStr">
         <is>
-          <t>GRECO</t>
+          <t>Multimedia Interactiva y Animación Digital</t>
         </is>
       </c>
       <c r="B12" s="11" t="n">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="C12" s="11" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="6" t="inlineStr">
         <is>
-          <t>GIIRA</t>
+          <t>GRECO</t>
         </is>
       </c>
       <c r="B13" s="6" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="C13" s="6" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="14">
@@ -1333,7 +1333,7 @@
     <row r="19">
       <c r="A19" s="6" t="inlineStr">
         <is>
-          <t>IAFT</t>
+          <t>GICOECOL</t>
         </is>
       </c>
       <c r="B19" s="6" t="n">
@@ -1359,7 +1359,7 @@
     <row r="21">
       <c r="A21" s="6" t="inlineStr">
         <is>
-          <t>GICOECOL</t>
+          <t>IAFT</t>
         </is>
       </c>
       <c r="B21" s="6" t="n">
@@ -1372,20 +1372,20 @@
     <row r="22">
       <c r="A22" s="11" t="inlineStr">
         <is>
-          <t>GITEM++</t>
+          <t>COMPLEX UD</t>
         </is>
       </c>
       <c r="B22" s="11" t="n">
+        <v>1</v>
+      </c>
+      <c r="C22" s="11" t="n">
         <v>0</v>
-      </c>
-      <c r="C22" s="11" t="n">
-        <v>1</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" s="6" t="inlineStr">
         <is>
-          <t>Bionanotecnología</t>
+          <t>LAMIC</t>
         </is>
       </c>
       <c r="B23" s="6" t="n">
@@ -1398,7 +1398,7 @@
     <row r="24">
       <c r="A24" s="11" t="inlineStr">
         <is>
-          <t>COMPLEX UD</t>
+          <t>Bionanotecnología</t>
         </is>
       </c>
       <c r="B24" s="11" t="n">
@@ -1411,66 +1411,66 @@
     <row r="25">
       <c r="A25" s="6" t="inlineStr">
         <is>
-          <t>DIMSI</t>
+          <t>CEPMS</t>
         </is>
       </c>
       <c r="B25" s="6" t="n">
+        <v>1</v>
+      </c>
+      <c r="C25" s="6" t="n">
         <v>0</v>
-      </c>
-      <c r="C25" s="6" t="n">
-        <v>1</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" s="11" t="inlineStr">
         <is>
-          <t>XUE</t>
+          <t>PROPROBOS</t>
         </is>
       </c>
       <c r="B26" s="11" t="n">
+        <v>1</v>
+      </c>
+      <c r="C26" s="11" t="n">
         <v>0</v>
-      </c>
-      <c r="C26" s="11" t="n">
-        <v>1</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" s="6" t="inlineStr">
         <is>
-          <t>CEPMS</t>
+          <t>DIMSI</t>
         </is>
       </c>
       <c r="B27" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="C27" s="6" t="n">
         <v>1</v>
-      </c>
-      <c r="C27" s="6" t="n">
-        <v>0</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" s="11" t="inlineStr">
         <is>
-          <t>PROPROBOS</t>
+          <t>XUE</t>
         </is>
       </c>
       <c r="B28" s="11" t="n">
+        <v>0</v>
+      </c>
+      <c r="C28" s="11" t="n">
         <v>1</v>
-      </c>
-      <c r="C28" s="11" t="n">
-        <v>0</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" s="6" t="inlineStr">
         <is>
-          <t>LAMIC</t>
+          <t>GITEM++</t>
         </is>
       </c>
       <c r="B29" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="C29" s="6" t="n">
         <v>1</v>
-      </c>
-      <c r="C29" s="6" t="n">
-        <v>0</v>
       </c>
     </row>
   </sheetData>
